--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B160"/>
+  <dimension ref="A1:B161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55.83203125" customWidth="1" min="1" max="1"/>
@@ -2377,6 +2377,18 @@
         </is>
       </c>
     </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Su</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B161"/>
+  <dimension ref="A1:B162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55.83203125" customWidth="1" min="1" max="1"/>
@@ -2389,6 +2389,18 @@
         </is>
       </c>
     </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Buy me a coffee</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Offrimi un caffè</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B162"/>
+  <dimension ref="A1:B163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55.83203125" customWidth="1" min="1" max="1"/>
@@ -2401,6 +2401,18 @@
         </is>
       </c>
     </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>File header is not standard CGATS (first line does not contain “CGATS” or “ISO28178”)</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>L’intestazione del file non è CGATS standard (la prima riga non contiene “CGATS” o “ISO28178”)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -1,32 +1,45 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr codeName="ThisWorkbook"/>
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
-    <sheet name="Translations" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
-      <sz val="12"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -41,13 +54,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -194,7 +208,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -229,7 +242,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -264,16 +276,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -395,46 +411,7 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
@@ -445,20 +422,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B163"/>
+  <dimension ref="A1:B171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="55.83203125" customWidth="1" min="1" max="1"/>
-    <col width="55.83203125" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>English</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Italian</t>
         </is>
@@ -599,1817 +576,1908 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Weighted</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sì</t>
+          <t>Ponderato</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>On</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Attivo</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Median</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Mediana</t>
+          <t>Disattivo</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Mean</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Sì</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>No</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sistema</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>Median</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Chiaro</t>
+          <t>Mediana</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Dark</t>
+          <t>Mean</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Scuro</t>
+          <t>Media</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>File Select</t>
+          <t>System</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Selezione file</t>
+          <t>Sistema</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Choose char data file</t>
+          <t>Light</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Scegli file dati</t>
+          <t>Chiaro</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Drop files here</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Rilascia i file qui</t>
+          <t>Scuro</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>or use button above</t>
+          <t>File Select</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>o usa il pulsante sopra</t>
+          <t>Selezione file</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sort files alphabetically</t>
+          <t>Choose char data file</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ordina alfabeticamente</t>
+          <t>Scegli file dati</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Explore</t>
+          <t>Drop files here</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Esplora</t>
+          <t>Rilascia i file qui</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Compare</t>
+          <t>or use button above</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Confronta</t>
+          <t>o usa il pulsante sopra</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Display File</t>
+          <t>Sort files alphabetically</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Mostra file</t>
+          <t>Ordina alfabeticamente</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Drag files here from</t>
+          <t>Explore</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Trascina i file qui da</t>
+          <t>Esplora</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>File Select pane or file system</t>
+          <t>Compare</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>selezione file o file system</t>
+          <t>Confronta</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3D Plot</t>
+          <t>Display File</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Grafico 3D</t>
+          <t>Mostra file</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Controls</t>
+          <t>Drag files here from</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Controlli</t>
+          <t>Trascina i file qui da</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Show gamut shell</t>
+          <t>File Select pane or file system</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Mostra guscio gamut</t>
+          <t>selezione file o file system</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Show data points</t>
+          <t>3D Plot</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Mostra punti dati</t>
+          <t>Grafico 3D</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Color by hue angle</t>
+          <t>Controls</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Colora per angolo di tinta</t>
+          <t>Controlli</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Color by value</t>
+          <t>Show gamut shell</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Colora per luminosità</t>
+          <t>Mostra guscio gamut</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Show spectral data when point selected</t>
+          <t>Show data points</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Mostra dati spettrali al clic</t>
+          <t>Mostra punti dati</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Computing…</t>
+          <t>Color by hue angle</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Calcolo…</t>
+          <t>Colora per angolo di tinta</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Gamut Slice (2D)</t>
+          <t>Color by value</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Sezione gamut (2D)</t>
+          <t>Colora per luminosità</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Axis:</t>
+          <t>Show spectral data when point selected</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Asse:</t>
+          <t>Mostra dati spettrali al clic</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Value:</t>
+          <t>Computing…</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Valore:</t>
+          <t>Calcolo…</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Bandwidth ±</t>
+          <t>Gamut Slice (2D)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Larghezza di banda ±</t>
+          <t>Sezione gamut (2D)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>No file loaded</t>
+          <t>Axis:</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Nessun file caricato</t>
+          <t>Asse:</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Tone Value</t>
+          <t>Value:</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Valore di tono</t>
+          <t>Valore:</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Tone Method</t>
+          <t>No file loaded</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Metodo tono</t>
+          <t>Nessun file caricato</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Spectral Murray-Davies</t>
+          <t>Tone Value</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Murray-Davies spettrale</t>
+          <t>Valore di tono</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Colour Tone Value (CTV)</t>
+          <t>Tone Method</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Valore di tono colore (CTV)</t>
+          <t>Metodo tono</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Filter</t>
+          <t>Spectral Murray-Davies</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Filtro</t>
+          <t>Murray-Davies spettrale</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Graph Type</t>
+          <t>Colour Tone Value (CTV)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Tipo di grafico</t>
+          <t>Valore di tono colore (CTV)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Transfer</t>
+          <t>Filter</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Trasferimento</t>
+          <t>Filtro</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Gain</t>
+          <t>Graph Type</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Guadagno</t>
+          <t>Tipo di grafico</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Ideal</t>
+          <t>Transfer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Ideale</t>
+          <t>Trasferimento</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Datasets</t>
+          <t>Gain</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Set di dati</t>
+          <t>Guadagno</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Validate</t>
+          <t>Ideal</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Valida</t>
+          <t>Ideale</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Comparison Table</t>
+          <t>Datasets</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Tabella di confronto</t>
+          <t>Set di dati</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Extract</t>
+          <t>Validate</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Estrai</t>
+          <t>Valida</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Restore</t>
+          <t>Comparison Table</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Ripristina</t>
+          <t>Tabella di confronto</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Export</t>
+          <t>Extract</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Esporta</t>
+          <t>Estrai</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Table</t>
+          <t>Restore</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Tabella dati</t>
+          <t>Ripristina</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Estimate</t>
+          <t>Export</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Stima</t>
+          <t>Esporta</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Primaries</t>
+          <t>Data Table</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Primari</t>
+          <t>Tabella dati</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Secondaries</t>
+          <t>Estimate</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Secondari</t>
+          <t>Stima</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CMY Grays</t>
+          <t>Primaries</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Grigi CMY</t>
+          <t>Primari</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>CMY Browns</t>
+          <t>Secondaries</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Bruni CMY</t>
+          <t>Secondari</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Solids Only</t>
+          <t>CMY Grays</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Solo pieni</t>
+          <t>Grigi CMY</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Remove paper white point</t>
+          <t>CMY Browns</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Rimuovi punto bianco carta</t>
+          <t>Bruni CMY</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Remove selected colorants from data.</t>
+          <t>Solids Only</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Rimuovi i coloranti selezionati dai dati.</t>
+          <t>Solo pieni</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Export File</t>
+          <t>Remove paper white point</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Esporta file</t>
+          <t>Rimuovi punto bianco carta</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Folder</t>
+          <t>Remove selected colorants from data.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Cartella</t>
+          <t>Rimuovi i coloranti selezionati dai dati.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>File name</t>
+          <t>Export File</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Nome file</t>
+          <t>Esporta file</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Format</t>
+          <t>Folder</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Formato</t>
+          <t>Cartella</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>File name</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Annulla</t>
+          <t>Nome file</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Save</t>
+          <t>Format</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Salva</t>
+          <t>Formato</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Select folder</t>
+          <t>Cancel</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Seleziona cartella</t>
+          <t>Annulla</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Browse for folder</t>
+          <t>Save</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Sfoglia cartelle</t>
+          <t>Salva</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Folder picker not supported in this browser</t>
+          <t>Select folder</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Selezione cartella non supportata da questo browser</t>
+          <t>Seleziona cartella</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Export destination folder…</t>
+          <t>Browse for folder</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Cartella di destinazione…</t>
+          <t>Sfoglia cartelle</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>File is neither CSV nor CGATS/ISO28178 format</t>
+          <t>Folder picker not supported in this browser</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Il file non è né CSV né CGATS/ISO28178</t>
+          <t>Selezione cartella non supportata da questo browser</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>✓ Valid</t>
+          <t>File Select: Drop or load files here to select.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>✓ Valido</t>
+          <t>Selezione file: trascina o carica file qui.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>LAB computed from spectral ({ill} / {obs} / {mc})</t>
+          <t>Drag-and-drop files from file system or File Select here</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>LAB calcolato dallo spettrale ({ill} / {obs} / {mc})</t>
+          <t>Trascina file dal file system o dalla selezione file</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Missing: {cols}</t>
+          <t>Click to sort</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Mancante: {cols}</t>
+          <t>Clicca per ordinare</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Loaded {n} rows.</t>
+          <t>Click to view spectral</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>{n} righe caricate.</t>
+          <t>Clicca per vedere lo spettro</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Loaded {n} rows, reduced to {m} rows by filtering duplicates ({method}).</t>
+          <t>Toggle controls</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>{n} righe caricate, ridotte a {m} filtrando i duplicati ({method}).</t>
+          <t>Mostra/nascondi controlli</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Device colorants:</t>
+          <t>Remove {item}</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Coloranti dispositivo:</t>
+          <t>Rimuovi {item}</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Device colorants: none</t>
+          <t>Click to toggle on/off</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Coloranti dispositivo: nessuno</t>
+          <t>Clicca per attivare/disattivare</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>File contains spectral data. Click on data points to display spectral graph.</t>
+          <t>Export destination folder…</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Il file contiene dati spettrali. Clicca sui punti per visualizzare il grafico.</t>
+          <t>Cartella di destinazione…</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Colorimetric only. No spectral data found in file.</t>
+          <t>File is neither CSV nor CGATS/ISO28178 format</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Solo colorimetrico. Nessun dato spettrale trovato nel file.</t>
+          <t>Il file non è né CSV né CGATS/ISO28178</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>{n} rows (after extract).</t>
+          <t>File header is not standard CGATS (first line does not contain “CGATS” or “ISO28178”)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>{n} righe (dopo estrazione).</t>
+          <t>L’intestazione del file non è CGATS standard (la prima riga non contiene “CGATS” o “ISO28178”)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>No comparable inkings between selected files.</t>
+          <t>✓ Valid</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Nessuna inchiostrazione confrontabile nei file selezionati.</t>
+          <t>✓ Valido</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>{n} matching data point</t>
+          <t>LAB computed from spectral ({ill} / {obs} / {mc})</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>{n} punto dati corrispondente</t>
+          <t>LAB calcolato dallo spettrale ({ill} / {obs} / {mc})</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>{n} matching data points</t>
+          <t>Missing: {cols}</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>{n} punti dati corrispondenti</t>
+          <t>Mancante: {cols}</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Mean {method}</t>
+          <t>Loaded {n} rows.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Media {method}</t>
+          <t>{n} righe caricate.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Min {method}</t>
+          <t>Loaded {n} rows, reduced to {m} rows by filtering duplicates ({method}).</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Min {method}</t>
+          <t>{n} righe caricate, ridotte a {m} filtrando i duplicati ({method}).</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Max {method}</t>
+          <t>Device colorants:</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Max {method}</t>
+          <t>Coloranti dispositivo:</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Std Dev</t>
+          <t>Device colorants: none</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Dev. std.</t>
+          <t>Coloranti dispositivo: nessuno</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Device Colorants</t>
+          <t>File contains spectral data. Click on data points to display spectral graph.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Coloranti dispositivo</t>
+          <t>Il file contiene dati spettrali. Clicca sui punti per visualizzare il grafico.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Difference</t>
+          <t>Colorimetric only. No spectral data found in file.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Differenza</t>
+          <t>Solo colorimetrico. Nessun dato spettrale trovato nel file.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Opacity</t>
+          <t>{n} rows (after extract).</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Opacità</t>
+          <t>{n} righe (dopo estrazione).</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>↻ Regenerate Shell</t>
+          <t>No comparable inkings between selected files.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>↻ Rigenera guscio</t>
+          <t>Nessuna inchiostrazione confrontabile nei file selezionati.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Mesh</t>
+          <t>{n} matching data point</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Maglia</t>
+          <t>{n} punto dati corrispondente</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Density</t>
+          <t>{n} matching data points</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Densità</t>
+          <t>{n} punti dati corrispondenti</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>Mean {method}</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Illuminazione</t>
+          <t>Media {method}</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ambient</t>
+          <t>Min {method}</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>ambient</t>
+          <t>Min {method}</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>diffuse</t>
+          <t>Max {method}</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>diffuse</t>
+          <t>Max {method}</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>specular</t>
+          <t>Std Dev</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>speculare</t>
+          <t>Dev. std.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>roughness</t>
+          <t>Points fitted</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>rugosità</t>
+          <t>Punti adattati</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Dataset Settings</t>
+          <t>Dataset {slot}</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Impostazioni set di dati</t>
+          <t>Set di dati {slot}</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Select to toggle file visibility:</t>
+          <t>Device Colorants</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Clicca per attivare/disattivare:</t>
+          <t>Coloranti dispositivo</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Toggle:</t>
+          <t>Difference</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Mostra:</t>
+          <t>Differenza</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Show:</t>
+          <t>Opacity</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Mostra:</t>
+          <t>Opacità</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Original</t>
+          <t>↻ Regenerate Shell</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Originale</t>
+          <t>↻ Rigenera guscio</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Modified</t>
+          <t>Mesh</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Modificato</t>
+          <t>Maglia</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>✕ Close</t>
+          <t>Density</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>✕ Chiudi</t>
+          <t>Densità</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Selected file is not loaded.</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Il file selezionato non è caricato.</t>
+          <t>Illuminazione</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Both files must be loaded.</t>
+          <t>ambient</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Entrambi i file devono essere caricati.</t>
+          <t>ambient</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>No K-only patches matched.</t>
+          <t>diffuse</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Nessuna patch K trovata.</t>
+          <t>diffuse</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>No CMY patches matched.</t>
+          <t>specular</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Nessuna patch CMY trovata.</t>
+          <t>speculare</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Missing CMYK device colorants in Dataset A{name}.</t>
+          <t>roughness</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Coloranti CMYK mancanti nel set di dati A{name}.</t>
+          <t>rugosità</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Missing L*a*b* data in Dataset A{name}.</t>
+          <t>Dataset Settings</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Dati L*a*b* mancanti nel set di dati A{name}.</t>
+          <t>Impostazioni set di dati</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Paper white patch (0,0,0,0) not found in Dataset A.</t>
+          <t>Select to toggle file visibility:</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Patch bianco carta (0,0,0,0) non trovata nel set di dati A.</t>
+          <t>Clicca per attivare/disattivare:</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>100K solid patch not found in Dataset A.</t>
+          <t>Toggle:</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Patch pieno 100K non trovata nel set di dati A.</t>
+          <t>Mostra:</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>100CMY solid patch not found in Dataset A.</t>
+          <t>Show:</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Patch pieno 100CMY non trovata nel set di dati A.</t>
+          <t>Mostra:</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>G7 Overall:</t>
+          <t>Original</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>G7 Complessivo:</t>
+          <t>Originale</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Scale</t>
+          <t>Modified</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Scala</t>
+          <t>Modificato</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Tolerance</t>
+          <t>✕ Close</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Tolleranza</t>
+          <t>✕ Chiudi</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>K (Black)</t>
+          <t>Selected file is not loaded.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>K (Nero)</t>
+          <t>Il file selezionato non è caricato.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>K patches ({n})</t>
+          <t>Both files must be loaded.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Patch K ({n})</t>
+          <t>Entrambi i file devono essere caricati.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>CMY patches ({n})</t>
+          <t>No K-only patches matched.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Patch CMY ({n})</t>
+          <t>Nessuna patch K trovata.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>K%</t>
+          <t>No CMY patches matched.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>K%</t>
+          <t>Nessuna patch CMY trovata.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>L* meas</t>
+          <t>Missing CMYK device colorants in Dataset A{name}.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>L* mis.</t>
+          <t>Coloranti CMYK mancanti nel set di dati A{name}.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>L* aim</t>
+          <t>Missing L*a*b* data in Dataset A{name}.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>L* obiettivo</t>
+          <t>Dati L*a*b* mancanti nel set di dati A{name}.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>meas</t>
+          <t>Paper white patch (0,0,0,0) not found in Dataset A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>mis.</t>
+          <t>Patch bianco carta (0,0,0,0) non trovata nel set di dati A.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>aim</t>
+          <t>100K solid patch not found in Dataset A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>obiet.</t>
+          <t>Patch pieno 100K non trovata nel set di dati A.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>No spectral data — switch to Colour Tone Value (CTV)</t>
+          <t>100CMY solid patch not found in Dataset A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Nessun dato spettrale — passare al valore di tono colore (CTV)</t>
+          <t>Patch pieno 100CMY non trovata nel set di dati A.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>No primary tone steps found.
-Needs rows with a single non-zero colorant.</t>
+          <t>G7 Overall:</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Nessuna fase di tono primario trovata.
-Servono righe con un unico colorante non zero.</t>
+          <t>G7 Complessivo:</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Tone Value Gain (%)</t>
+          <t>Scale</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Guadagno valore di tono (%)</t>
+          <t>Scala</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Tone Value (%)</t>
+          <t>Tolerance</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Valore di tono (%)</t>
+          <t>Tolleranza</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Input (%)</t>
+          <t>K (Black)</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Ingresso (%)</t>
+          <t>K (Nero)</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Model fit — degree {deg}, {n} points</t>
+          <t>K patches ({n})</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Adattamento modello — grado {deg}, {n} punti</t>
+          <t>Patch K ({n})</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>↻ Regenerate</t>
+          <t>CMY patches ({n})</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>↻ Rigenera</t>
+          <t>Patch CMY ({n})</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Input colorant</t>
+          <t>K%</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Colorante
-ingresso</t>
+          <t>K%</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Nearest
-in dataset</t>
+          <t>L* meas</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Più vicino
-nel set</t>
+          <t>L* mis.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>L* aim</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Modello</t>
+          <t>L* obiettivo</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Computing…</t>
+          <t>meas</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Calcolo…</t>
+          <t>mis.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Model fit failed: {msg}</t>
+          <t>aim</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Adattamento modello fallito: {msg}</t>
+          <t>obiet.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Retry</t>
+          <t>No spectral data — switch to Colour Tone Value (CTV)</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Riprova</t>
+          <t>Nessun dato spettrale — passare al valore di tono colore (CTV)</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Click on L*a*b* color to display spectral graph.</t>
+          <t>No primary tone steps found.\nNeeds rows with a single non-zero colorant.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Clicca su un colore L*a*b* per visualizzare il grafico spettrale.</t>
+          <t>Nessuna fase di tono primario trovata.\nServono righe con un unico colorante non zero.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Scroll to top</t>
+          <t>Tone Value Gain (%)</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Torna su</t>
+          <t>Guadagno valore di tono (%)</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Help</t>
+          <t>Tone Value (%)</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Guida</t>
+          <t>Valore di tono (%)</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>About CharData</t>
+          <t>Input (%)</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Informazioni su CharData</t>
+          <t>Ingresso (%)</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Support on Ko-fi</t>
+          <t>Model fit — degree {deg}, {n} points</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Sostieni su Ko-fi</t>
+          <t>Adattamento modello — grado {deg}, {n} punti</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>CharData is free for the color community. If it helps you, a small Ko-fi donation helps keep it running.</t>
+          <t>↻ Regenerate</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>CharData è gratuito per la comunità del colore. Un piccolo contributo Ko-fi aiuta a mantenerlo attivo.</t>
+          <t>↻ Rigenera</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Points fitted</t>
+          <t>Input\ncolorant</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Punti adattati</t>
+          <t>Colorante\ningresso</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Dataset {slot}</t>
+          <t>Nearest\nin dataset</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Set di dati {slot}</t>
+          <t>Più vicino\nnel set</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>File Select: Drop or load files here to select.</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Selezione file: trascina o carica file qui.</t>
+          <t>Modello</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Drag-and-drop files from file system or File Select here</t>
+          <t>Computing…</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Trascina file dal file system o dalla selezione file</t>
+          <t>Calcolo…</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Click to sort</t>
+          <t>Calculating tone values…</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Clicca per ordinare</t>
+          <t>Calculating tone values…</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Click to view spectral</t>
+          <t>Estimating model…</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Clicca per vedere lo spettro</t>
+          <t>Estimating model…</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Toggle controls</t>
+          <t>Building 3D gamut…</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Mostra/nascondi controlli</t>
+          <t>Building 3D gamut…</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Remove {item}</t>
+          <t>Computing 2D slice…</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Rimuovi {item}</t>
+          <t>Computing 2D slice…</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Click to toggle on/off</t>
+          <t>Rendering…</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Clicca per attivare/disattivare</t>
+          <t>Rendering…</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Model fit failed: {msg}</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Su</t>
+          <t>Adattamento modello fallito: {msg}</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Buy me a coffee</t>
+          <t>Retry</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Offrimi un caffè</t>
+          <t>Riprova</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>File header is not standard CGATS (first line does not contain “CGATS” or “ISO28178”)</t>
+          <t>Click on L*a*b* color to display spectral graph.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>L’intestazione del file non è CGATS standard (la prima riga non contiene “CGATS” o “ISO28178”)</t>
+          <t>Clicca su un colore L*a*b* per visualizzare il grafico spettrale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Scroll to top</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Torna su</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Su</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Help</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Guida</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>About CharData</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Informazioni su CharData</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Support on Ko-fi</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Sostieni su Ko-fi</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Buy me a coffee</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Offrimi un caffè</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Reflectance</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Riflettanza</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>CharData is free for the color community. If it helps you, a small Ko-fi donation helps keep it running.</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>CharData è gratuito per la comunità del colore. Un piccolo contributo Ko-fi aiuta a mantenerlo attivo.</t>
         </is>
       </c>
     </row>

--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B178"/>
+  <dimension ref="A1:B181"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1825,9 +1825,33 @@
         <v>Profilo ICC non valido (signature dell’header mancante).</v>
       </c>
     </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>Standard datasets</v>
+      </c>
+      <c r="B179" t="str">
+        <v>Set di dati standard</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
+        <v>Loading…</v>
+      </c>
+      <c r="B180" t="str">
+        <v>Caricamento…</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="str">
+        <v>Failed to load list</v>
+      </c>
+      <c r="B181" t="str">
+        <v>Caricamento dell'elenco non riuscito</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B178"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B181"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -585,12 +585,12 @@
     </row>
     <row r="24" xml:space="preserve">
       <c r="A24" t="str" xml:space="preserve">
-        <v xml:space="preserve">Select files:
-characterization data or ICC profiles</v>
+        <v xml:space="preserve">characterization data
+or ICC profiles</v>
       </c>
       <c r="B24" t="str" xml:space="preserve">
-        <v xml:space="preserve">Seleziona file:
-dati di caratterizzazione o profili ICC</v>
+        <v xml:space="preserve">dati di caratterizzazione
+o profili ICC</v>
       </c>
     </row>
     <row r="25">

--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B181"/>
+  <dimension ref="A1:B185"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1849,9 +1849,41 @@
         <v>Caricamento dell'elenco non riuscito</v>
       </c>
     </row>
+    <row r="182">
+      <c r="A182" t="str">
+        <v>Thickness:</v>
+      </c>
+      <c r="B182" t="str">
+        <v>Spessore:</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v>Fall-off:</v>
+      </c>
+      <c r="B183" t="str">
+        <v>Attenuazione:</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="str">
+        <v>Hard</v>
+      </c>
+      <c r="B184" t="str">
+        <v>Netto</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="str">
+        <v>Soft</v>
+      </c>
+      <c r="B185" t="str">
+        <v>Morbido</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B181"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B185"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B185"/>
+  <dimension ref="A1:B189"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1881,9 +1881,41 @@
         <v>Morbido</v>
       </c>
     </row>
+    <row r="186">
+      <c r="A186" t="str">
+        <v>G7 validation is not available for ICC profiles.</v>
+      </c>
+      <c r="B186" t="str">
+        <v>La validazione G7 non è disponibile per i profili ICC.</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="str">
+        <v>ICC vs ICC comparison requires CMYK profiles.</v>
+      </c>
+      <c r="B187" t="str">
+        <v>Il confronto ICC vs ICC richiede profili CMYK.</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="str">
+        <v>Dataset B does not contain colorants matching ICC profile A.</v>
+      </c>
+      <c r="B188" t="str">
+        <v>Il dataset B non contiene coloranti corrispondenti al profilo ICC A.</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
+        <v>Dataset A does not contain colorants matching ICC profile B.</v>
+      </c>
+      <c r="B189" t="str">
+        <v>Il dataset A non contiene coloranti corrispondenti al profilo ICC B.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B185"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B189"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B189"/>
+  <dimension ref="A1:B192"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1913,9 +1913,33 @@
         <v>Il dataset A non contiene coloranti corrispondenti al profilo ICC B.</v>
       </c>
     </row>
+    <row r="190">
+      <c r="A190" t="str">
+        <v>Header</v>
+      </c>
+      <c r="B190" t="str">
+        <v>Intestazione</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>Tags</v>
+      </c>
+      <c r="B191" t="str">
+        <v>Tag</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>Loading ICC viewer…</v>
+      </c>
+      <c r="B192" t="str">
+        <v>Caricamento del visualizzatore ICC…</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B189"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B192"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B192"/>
+  <dimension ref="A1:B193"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1937,9 +1937,17 @@
         <v>Caricamento del visualizzatore ICC…</v>
       </c>
     </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>Launch editor</v>
+      </c>
+      <c r="B193" t="str">
+        <v>Apri editor</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B192"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B193"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B193"/>
+  <dimension ref="A1:B195"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1945,9 +1945,25 @@
         <v>Apri editor</v>
       </c>
     </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>All data stays local to browser</v>
+      </c>
+      <c r="B194" t="str">
+        <v>Tutti i dati restano locali nel browser</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>Free browser-resident online tool</v>
+      </c>
+      <c r="B195" t="str">
+        <v>Strumento online gratuito che funziona nel browser</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B193"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B195"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -1561,12 +1561,14 @@
         <v>Nessun dato spettrale — passare al valore di tono colore (CTV)</v>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" t="str">
-        <v>No primary tone steps found.\nNeeds rows with a single non-zero colorant.</v>
-      </c>
-      <c r="B146" t="str">
-        <v>Nessuna fase di tono primario trovata.\nServono righe con un unico colorante non zero.</v>
+    <row r="146" xml:space="preserve">
+      <c r="A146" t="str" xml:space="preserve">
+        <v xml:space="preserve">No primary tone steps found.
+Needs rows with a single non-zero colorant.</v>
+      </c>
+      <c r="B146" t="str" xml:space="preserve">
+        <v xml:space="preserve">Nessuna fase di tono primario trovata.
+Servono righe con un unico colorante non zero.</v>
       </c>
     </row>
     <row r="147">
@@ -1609,20 +1611,24 @@
         <v>↻ Rigenera</v>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" t="str">
-        <v>Input\ncolorant</v>
-      </c>
-      <c r="B152" t="str">
-        <v>Colorante\ningresso</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="str">
-        <v>Nearest\nin dataset</v>
-      </c>
-      <c r="B153" t="str">
-        <v>Più vicino\nnel set</v>
+    <row r="152" xml:space="preserve">
+      <c r="A152" t="str" xml:space="preserve">
+        <v xml:space="preserve">Input
+colorant</v>
+      </c>
+      <c r="B152" t="str" xml:space="preserve">
+        <v xml:space="preserve">Colorante
+ingresso</v>
+      </c>
+    </row>
+    <row r="153" xml:space="preserve">
+      <c r="A153" t="str" xml:space="preserve">
+        <v xml:space="preserve">Nearest
+in dataset</v>
+      </c>
+      <c r="B153" t="str" xml:space="preserve">
+        <v xml:space="preserve">Più vicino
+nel set</v>
       </c>
     </row>
     <row r="154">

--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B195"/>
+  <dimension ref="A1:B205"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1967,9 +1967,89 @@
         <v>Strumento online gratuito che funziona nel browser</v>
       </c>
     </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>Image</v>
+      </c>
+      <c r="B196" t="str">
+        <v>Immagine</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>Load Image</v>
+      </c>
+      <c r="B197" t="str">
+        <v>Carica immagine</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>Bind image to dataset</v>
+      </c>
+      <c r="B198" t="str">
+        <v>Associa l’immagine al dataset</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>Remove image</v>
+      </c>
+      <c r="B199" t="str">
+        <v>Rimuovi immagine</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>Image color space: {cs} {src}</v>
+      </c>
+      <c r="B200" t="str">
+        <v>Spazio colore immagine: {cs} {src}</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>Bound to {name} — {n} points</v>
+      </c>
+      <c r="B201" t="str">
+        <v>Associato a {name} — {n} punti</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>Lab image — {n} points</v>
+      </c>
+      <c r="B202" t="str">
+        <v>Immagine Lab — {n} punti</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>Cannot bind: image is {img} but Dataset {slot} is {family}.</v>
+      </c>
+      <c r="B203" t="str">
+        <v>Associazione impossibile: l’immagine è {img} ma il Dataset {slot} è {family}.</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>Unsupported image format. Use PNG, JPEG, or TIFF.</v>
+      </c>
+      <c r="B204" t="str">
+        <v>Formato immagine non supportato. Usa PNG, JPEG o TIFF.</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>“{name}” is too large ({mb} MB). Maximum image size is {max} MB.</v>
+      </c>
+      <c r="B205" t="str">
+        <v>“{name}” è troppo grande ({mb} MB). Dimensione massima: {max} MB.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B195"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B205"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B205"/>
+  <dimension ref="A1:B224"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2033,10 +2033,10 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Unsupported image format. Use PNG, JPEG, or TIFF.</v>
+        <v>Unsupported image format. Use PNG, JPEG, TIFF, BMP, GIF, or PDF.</v>
       </c>
       <c r="B204" t="str">
-        <v>Formato immagine non supportato. Usa PNG, JPEG o TIFF.</v>
+        <v>Formato immagine non supportato. Usa PNG, JPEG, TIFF, BMP, GIF o PDF.</v>
       </c>
     </row>
     <row r="205">
@@ -2047,9 +2047,161 @@
         <v>“{name}” è troppo grande ({mb} MB). Dimensione massima: {max} MB.</v>
       </c>
     </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>Embedded: {name}</v>
+      </c>
+      <c r="B206" t="str">
+        <v>Incorporato: {name}</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>Decoding image…</v>
+      </c>
+      <c r="B207" t="str">
+        <v>Decodifica immagine in corso…</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>Image file is too small or corrupt.</v>
+      </c>
+      <c r="B208" t="str">
+        <v>Il file immagine è troppo piccolo o danneggiato.</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>TIFF decoder library failed to load.</v>
+      </c>
+      <c r="B209" t="str">
+        <v>Caricamento della libreria di decodifica TIFF non riuscito.</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>Selected dataset model is still loading — try again in a moment.</v>
+      </c>
+      <c r="B210" t="str">
+        <v>Il modello del dataset selezionato è ancora in caricamento — riprova tra un istante.</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>Image decode failed.</v>
+      </c>
+      <c r="B211" t="str">
+        <v>Decodifica immagine non riuscita.</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>Dataset {slot} is not loaded.</v>
+      </c>
+      <c r="B212" t="str">
+        <v>Il Dataset {slot} non è caricato.</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>Embedded profile is no longer available.</v>
+      </c>
+      <c r="B213" t="str">
+        <v>Il profilo incorporato non è più disponibile.</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
+        <v>(from embedded ICC)</v>
+      </c>
+      <c r="B214" t="str">
+        <v>(dall’ICC incorporato)</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="str">
+        <v>(TIFF Lab)</v>
+      </c>
+      <c r="B215" t="str">
+        <v>(TIFF Lab)</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="str">
+        <v>(inferred from channels)</v>
+      </c>
+      <c r="B216" t="str">
+        <v>(dedotto dai canali)</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="str">
+        <v>{n} representative points after binning + dedupe</v>
+      </c>
+      <c r="B217" t="str">
+        <v>{n} punti rappresentativi dopo binning + deduplica</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="str">
+        <v>PDF support is limited to single-image Photoshop PDFs. Save as TIFF, JPEG, PNG, BMP, or GIF for other PDF content.</v>
+      </c>
+      <c r="B218" t="str">
+        <v>Il supporto PDF è limitato ai PDF Photoshop con una sola immagine. Salva come TIFF, JPEG, PNG, BMP o GIF per altri contenuti PDF.</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="str">
+        <v>Encrypted PDFs are not supported.</v>
+      </c>
+      <c r="B219" t="str">
+        <v>I PDF crittografati non sono supportati.</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="str">
+        <v>Only single-page Photoshop PDFs are supported.</v>
+      </c>
+      <c r="B220" t="str">
+        <v>Sono supportati solo i PDF Photoshop di una sola pagina.</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="str">
+        <v>PDF structure could not be parsed.</v>
+      </c>
+      <c r="B221" t="str">
+        <v>Impossibile analizzare la struttura del PDF.</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="str">
+        <v>No image found inside the PDF.</v>
+      </c>
+      <c r="B222" t="str">
+        <v>Nessuna immagine trovata nel PDF.</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="str">
+        <v>PDF colour space is not supported. Use Gray, RGB, CMYK, or an ICC-based profile.</v>
+      </c>
+      <c r="B223" t="str">
+        <v>Spazio colore PDF non supportato. Usa Grigio, RGB, CMYK o un profilo ICC.</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="str">
+        <v>PDF image filter is not supported. Re-save the PDF with JPEG or ZIP compression.</v>
+      </c>
+      <c r="B224" t="str">
+        <v>Filtro immagine PDF non supportato. Salva nuovamente il PDF con compressione JPEG o ZIP.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B205"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B224"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B224"/>
+  <dimension ref="A1:B242"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2199,9 +2199,153 @@
         <v>Filtro immagine PDF non supportato. Salva nuovamente il PDF con compressione JPEG o ZIP.</v>
       </c>
     </row>
+    <row r="225">
+      <c r="A225" t="str">
+        <v>Close file select</v>
+      </c>
+      <c r="B225" t="str">
+        <v>Chiudi selezione file</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="str">
+        <v>Drag to resize</v>
+      </c>
+      <c r="B226" t="str">
+        <v>Trascina per ridimensionare</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="str">
+        <v>Contact</v>
+      </c>
+      <c r="B227" t="str">
+        <v>Contatto</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="str">
+        <v>Remove file</v>
+      </c>
+      <c r="B228" t="str">
+        <v>Rimuovi file</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="str">
+        <v>Rendering intent:</v>
+      </c>
+      <c r="B229" t="str">
+        <v>Intento di rendering:</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="str">
+        <v>Perceptual</v>
+      </c>
+      <c r="B230" t="str">
+        <v>Percettivo</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="str">
+        <v>Relative Colorimetric</v>
+      </c>
+      <c r="B231" t="str">
+        <v>Colorimetrico relativo</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="str">
+        <v>Saturation</v>
+      </c>
+      <c r="B232" t="str">
+        <v>Saturazione</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="str">
+        <v>Absolute Colorimetric</v>
+      </c>
+      <c r="B233" t="str">
+        <v>Colorimetrico assoluto</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="str">
+        <v>System default ({lang})</v>
+      </c>
+      <c r="B234" t="str">
+        <v>Predefinito di sistema ({lang})</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="str">
+        <v>ICC load error: {msg}</v>
+      </c>
+      <c r="B235" t="str">
+        <v>Errore di caricamento ICC: {msg}</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="str">
+        <v>Could not parse ICC profile: {msg}</v>
+      </c>
+      <c r="B236" t="str">
+        <v>Impossibile analizzare il profilo ICC: {msg}</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="str">
+        <v>Popup blocked — allow popups for this site to launch the editor.</v>
+      </c>
+      <c r="B237" t="str">
+        <v>Popup bloccato — consenti i popup per questo sito per avviare l’editor.</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="str">
+        <v>Failed to load {name}: {msg}</v>
+      </c>
+      <c r="B238" t="str">
+        <v>Caricamento di {name} non riuscito: {msg}</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="str">
+        <v>Color space</v>
+      </c>
+      <c r="B239" t="str">
+        <v>Spazio colore</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="str">
+        <v>Device class</v>
+      </c>
+      <c r="B240" t="str">
+        <v>Classe dispositivo</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="str">
+        <v>Colorants</v>
+      </c>
+      <c r="B241" t="str">
+        <v>Coloranti</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="str">
+        <v>Rendering intents</v>
+      </c>
+      <c r="B242" t="str">
+        <v>Intenti di rendering</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B224"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B242"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B242"/>
+  <dimension ref="A1:B244"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2343,9 +2343,25 @@
         <v>Intenti di rendering</v>
       </c>
     </row>
+    <row r="243">
+      <c r="A243" t="str">
+        <v>ICC A2B Evaluation</v>
+      </c>
+      <c r="B243" t="str">
+        <v>Valutazione ICC A2B</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="str">
+        <v>ICC Output</v>
+      </c>
+      <c r="B244" t="str">
+        <v>Uscita ICC</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B242"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B244"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B244"/>
+  <dimension ref="A1:B248"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2359,9 +2359,41 @@
         <v>Uscita ICC</v>
       </c>
     </row>
+    <row r="245">
+      <c r="A245" t="str">
+        <v>Image detail</v>
+      </c>
+      <c r="B245" t="str">
+        <v>Dettaglio immagine</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="str">
+        <v>Coarse</v>
+      </c>
+      <c r="B246" t="str">
+        <v>Grossolano</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="str">
+        <v>Standard</v>
+      </c>
+      <c r="B247" t="str">
+        <v>Standard</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="str">
+        <v>Fine</v>
+      </c>
+      <c r="B248" t="str">
+        <v>Fine</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B244"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B248"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B248"/>
+  <dimension ref="A1:B263"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2391,9 +2391,129 @@
         <v>Fine</v>
       </c>
     </row>
+    <row r="249">
+      <c r="A249" t="str">
+        <v>Subscribe</v>
+      </c>
+      <c r="B249" t="str">
+        <v>Iscriviti</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="str">
+        <v>Get notified about new chardata releases</v>
+      </c>
+      <c r="B250" t="str">
+        <v>Ricevi notifiche sulle nuove versioni di chardata</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="str">
+        <v>Get notified about new releases</v>
+      </c>
+      <c r="B251" t="str">
+        <v>Ricevi notifiche sulle nuove versioni</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B252" t="str">
+        <v>Chiudi</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="str">
+        <v>We’ll email you when a new major or minor chardata release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+      </c>
+      <c r="B253" t="str">
+        <v>Ti invieremo un’e-mail quando esce una nuova versione maggiore o minore di chardata. Le versioni patch sono escluse. Il tuo indirizzo viene verificato manualmente prima di essere aggiunto.</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="str">
+        <v>Email address</v>
+      </c>
+      <c r="B254" t="str">
+        <v>Indirizzo e-mail</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="str">
+        <v>you@example.com</v>
+      </c>
+      <c r="B255" t="str">
+        <v>tu@esempio.com</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="str">
+        <v>How will you use chardata?</v>
+      </c>
+      <c r="B256" t="str">
+        <v>Come utilizzerai chardata?</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="str">
+        <v>(optional)</v>
+      </c>
+      <c r="B257" t="str">
+        <v>(opzionale)</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="str">
+        <v>e.g. evaluating ICC profiles for press calibration</v>
+      </c>
+      <c r="B258" t="str">
+        <v>p. es. valutare profili ICC per la calibrazione di stampa</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="str">
+        <v>I agree to receive emails about chardata releases. I can unsubscribe at any time.</v>
+      </c>
+      <c r="B259" t="str">
+        <v>Accetto di ricevere e-mail sulle versioni di chardata. Posso annullare l’iscrizione in qualsiasi momento.</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="str">
+        <v>Subscribe</v>
+      </c>
+      <c r="B260" t="str">
+        <v>Iscriviti</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="str">
+        <v>Thanks — we’ll be in touch.</v>
+      </c>
+      <c r="B261" t="str">
+        <v>Grazie — ti ricontatteremo.</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="str">
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new chardata release ships.</v>
+      </c>
+      <c r="B262" t="str">
+        <v>Una volta approvato, riceverai un’e-mail di benvenuto. In seguito, ti contatteremo solo quando uscirà una nuova versione di chardata.</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B263" t="str">
+        <v>Chiudi</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B248"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B263"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B263"/>
+  <dimension ref="A1:B264"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2511,9 +2511,17 @@
         <v>Chiudi</v>
       </c>
     </row>
+    <row r="264">
+      <c r="A264" t="str">
+        <v>Privacy notice</v>
+      </c>
+      <c r="B264" t="str">
+        <v>Informativa sulla privacy</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B263"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B264"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -2097,10 +2097,10 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Dataset {slot} is not loaded.</v>
+        <v>No color dataset loaded.</v>
       </c>
       <c r="B212" t="str">
-        <v>Il Dataset {slot} non è caricato.</v>
+        <v>Nessun set di dati colorimetrici caricato.</v>
       </c>
     </row>
     <row r="213">

--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -1897,10 +1897,10 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>ICC vs ICC comparison requires CMYK profiles.</v>
+        <v>ICC vs ICC comparison requires identical colorant lists. Profile A: {a}. Profile B: {b}.</v>
       </c>
       <c r="B187" t="str">
-        <v>Il confronto ICC vs ICC richiede profili CMYK.</v>
+        <v>Il confronto ICC vs ICC richiede liste di coloranti identiche. Profilo A: {a}. Profilo B: {b}.</v>
       </c>
     </row>
     <row r="188">

--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B264"/>
+  <dimension ref="A1:B269"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2519,9 +2519,49 @@
         <v>Informativa sulla privacy</v>
       </c>
     </row>
+    <row r="265">
+      <c r="A265" t="str">
+        <v>Measurement-only data (no device colorants): 3D and 2D-slice point cloud, data table, and label-matched compare are available; gamut shell, extract, tone value, estimate, and validation are disabled.</v>
+      </c>
+      <c r="B265" t="str">
+        <v>Solo dati di misura (nessun colorante dispositivo): nuvola di punti 3D e sezione 2D, tabella dati e confronto per etichetta disponibili; guscio gamut, estrazione, valore di tono, stima e validazione disabilitati.</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="str">
+        <v>Sample</v>
+      </c>
+      <c r="B266" t="str">
+        <v>Campione</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="str">
+        <v>CxF file is not well-formed XML.</v>
+      </c>
+      <c r="B267" t="str">
+        <v>Il file CxF non è un XML ben formato.</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="str">
+        <v>CxF file contains no colour objects.</v>
+      </c>
+      <c r="B268" t="str">
+        <v>Il file CxF non contiene oggetti colore.</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="str">
+        <v>CxF file contains no CIELab or spectral colour values.</v>
+      </c>
+      <c r="B269" t="str">
+        <v>Il file CxF non contiene valori di colore CIELab o spettrali.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B264"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B269"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B269"/>
+  <dimension ref="A1:B268"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1275,87 +1275,87 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>↻ Regenerate Shell</v>
+        <v>Mesh</v>
       </c>
       <c r="B110" t="str">
-        <v>↻ Rigenera guscio</v>
+        <v>Maglia</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Mesh</v>
+        <v>Density</v>
       </c>
       <c r="B111" t="str">
-        <v>Maglia</v>
+        <v>Densità</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Density</v>
+        <v>Lighting</v>
       </c>
       <c r="B112" t="str">
-        <v>Densità</v>
+        <v>Illuminazione</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Lighting</v>
+        <v>ambient</v>
       </c>
       <c r="B113" t="str">
-        <v>Illuminazione</v>
+        <v>ambient</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>ambient</v>
+        <v>diffuse</v>
       </c>
       <c r="B114" t="str">
-        <v>ambient</v>
+        <v>diffuse</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>diffuse</v>
+        <v>specular</v>
       </c>
       <c r="B115" t="str">
-        <v>diffuse</v>
+        <v>speculare</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>specular</v>
+        <v>roughness</v>
       </c>
       <c r="B116" t="str">
-        <v>speculare</v>
+        <v>rugosità</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>roughness</v>
+        <v>Dataset Settings</v>
       </c>
       <c r="B117" t="str">
-        <v>rugosità</v>
+        <v>Impostazioni set di dati</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Dataset Settings</v>
+        <v>Select to toggle file visibility:</v>
       </c>
       <c r="B118" t="str">
-        <v>Impostazioni set di dati</v>
+        <v>Clicca per attivare/disattivare:</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Select to toggle file visibility:</v>
+        <v>Toggle:</v>
       </c>
       <c r="B119" t="str">
-        <v>Clicca per attivare/disattivare:</v>
+        <v>Mostra:</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Toggle:</v>
+        <v>Show:</v>
       </c>
       <c r="B120" t="str">
         <v>Mostra:</v>
@@ -1363,1205 +1363,1197 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Show:</v>
+        <v>Original</v>
       </c>
       <c r="B121" t="str">
-        <v>Mostra:</v>
+        <v>Originale</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Original</v>
+        <v>Modified</v>
       </c>
       <c r="B122" t="str">
-        <v>Originale</v>
+        <v>Modificato</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Modified</v>
+        <v>✕ Close</v>
       </c>
       <c r="B123" t="str">
-        <v>Modificato</v>
+        <v>✕ Chiudi</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>✕ Close</v>
+        <v>Selected file is not loaded.</v>
       </c>
       <c r="B124" t="str">
-        <v>✕ Chiudi</v>
+        <v>Il file selezionato non è caricato.</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Selected file is not loaded.</v>
+        <v>Both files must be loaded.</v>
       </c>
       <c r="B125" t="str">
-        <v>Il file selezionato non è caricato.</v>
+        <v>Entrambi i file devono essere caricati.</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Both files must be loaded.</v>
+        <v>No K-only patches matched.</v>
       </c>
       <c r="B126" t="str">
-        <v>Entrambi i file devono essere caricati.</v>
+        <v>Nessuna patch K trovata.</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>No K-only patches matched.</v>
+        <v>No CMY patches matched.</v>
       </c>
       <c r="B127" t="str">
-        <v>Nessuna patch K trovata.</v>
+        <v>Nessuna patch CMY trovata.</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>No CMY patches matched.</v>
+        <v>Missing CMYK device colorants in Dataset A{name}.</v>
       </c>
       <c r="B128" t="str">
-        <v>Nessuna patch CMY trovata.</v>
+        <v>Coloranti CMYK mancanti nel set di dati A{name}.</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Missing CMYK device colorants in Dataset A{name}.</v>
+        <v>Missing L*a*b* data in Dataset A{name}.</v>
       </c>
       <c r="B129" t="str">
-        <v>Coloranti CMYK mancanti nel set di dati A{name}.</v>
+        <v>Dati L*a*b* mancanti nel set di dati A{name}.</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Missing L*a*b* data in Dataset A{name}.</v>
+        <v>Paper white patch (0,0,0,0) not found in Dataset A.</v>
       </c>
       <c r="B130" t="str">
-        <v>Dati L*a*b* mancanti nel set di dati A{name}.</v>
+        <v>Patch bianco carta (0,0,0,0) non trovata nel set di dati A.</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Paper white patch (0,0,0,0) not found in Dataset A.</v>
+        <v>100K solid patch not found in Dataset A.</v>
       </c>
       <c r="B131" t="str">
-        <v>Patch bianco carta (0,0,0,0) non trovata nel set di dati A.</v>
+        <v>Patch pieno 100K non trovata nel set di dati A.</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>100K solid patch not found in Dataset A.</v>
+        <v>100CMY solid patch not found in Dataset A.</v>
       </c>
       <c r="B132" t="str">
-        <v>Patch pieno 100K non trovata nel set di dati A.</v>
+        <v>Patch pieno 100CMY non trovata nel set di dati A.</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>100CMY solid patch not found in Dataset A.</v>
+        <v>G7 Overall:</v>
       </c>
       <c r="B133" t="str">
-        <v>Patch pieno 100CMY non trovata nel set di dati A.</v>
+        <v>G7 Complessivo:</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>G7 Overall:</v>
+        <v>Scale</v>
       </c>
       <c r="B134" t="str">
-        <v>G7 Complessivo:</v>
+        <v>Scala</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Scale</v>
+        <v>Tolerance</v>
       </c>
       <c r="B135" t="str">
-        <v>Scala</v>
+        <v>Tolleranza</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Tolerance</v>
+        <v>K (Black)</v>
       </c>
       <c r="B136" t="str">
-        <v>Tolleranza</v>
+        <v>K (Nero)</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>K (Black)</v>
+        <v>K patches ({n})</v>
       </c>
       <c r="B137" t="str">
-        <v>K (Nero)</v>
+        <v>Patch K ({n})</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>K patches ({n})</v>
+        <v>CMY patches ({n})</v>
       </c>
       <c r="B138" t="str">
-        <v>Patch K ({n})</v>
+        <v>Patch CMY ({n})</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>CMY patches ({n})</v>
+        <v>K%</v>
       </c>
       <c r="B139" t="str">
-        <v>Patch CMY ({n})</v>
+        <v>K%</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>K%</v>
+        <v>L* meas</v>
       </c>
       <c r="B140" t="str">
-        <v>K%</v>
+        <v>L* mis.</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>L* meas</v>
+        <v>L* aim</v>
       </c>
       <c r="B141" t="str">
-        <v>L* mis.</v>
+        <v>L* obiettivo</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>L* aim</v>
+        <v>meas</v>
       </c>
       <c r="B142" t="str">
-        <v>L* obiettivo</v>
+        <v>mis.</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>meas</v>
+        <v>aim</v>
       </c>
       <c r="B143" t="str">
-        <v>mis.</v>
+        <v>obiet.</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>aim</v>
+        <v>No spectral data — switch to Colour Tone Value (CTV)</v>
       </c>
       <c r="B144" t="str">
-        <v>obiet.</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="str">
-        <v>No spectral data — switch to Colour Tone Value (CTV)</v>
-      </c>
-      <c r="B145" t="str">
         <v>Nessun dato spettrale — passare al valore di tono colore (CTV)</v>
       </c>
     </row>
-    <row r="146" xml:space="preserve">
-      <c r="A146" t="str" xml:space="preserve">
+    <row r="145" xml:space="preserve">
+      <c r="A145" t="str" xml:space="preserve">
         <v xml:space="preserve">No primary tone steps found.
 Needs rows with a single non-zero colorant.</v>
       </c>
-      <c r="B146" t="str" xml:space="preserve">
+      <c r="B145" t="str" xml:space="preserve">
         <v xml:space="preserve">Nessuna fase di tono primario trovata.
 Servono righe con un unico colorante non zero.</v>
       </c>
     </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>Tone Value Gain (%)</v>
+      </c>
+      <c r="B146" t="str">
+        <v>Guadagno valore di tono (%)</v>
+      </c>
+    </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Tone Value Gain (%)</v>
+        <v>Tone Value (%)</v>
       </c>
       <c r="B147" t="str">
-        <v>Guadagno valore di tono (%)</v>
+        <v>Valore di tono (%)</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Tone Value (%)</v>
+        <v>Input (%)</v>
       </c>
       <c r="B148" t="str">
-        <v>Valore di tono (%)</v>
+        <v>Ingresso (%)</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Input (%)</v>
+        <v>Model fit — degree {deg}, {n} points</v>
       </c>
       <c r="B149" t="str">
-        <v>Ingresso (%)</v>
+        <v>Adattamento modello — grado {deg}, {n} punti</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Model fit — degree {deg}, {n} points</v>
+        <v>↻ Regenerate</v>
       </c>
       <c r="B150" t="str">
-        <v>Adattamento modello — grado {deg}, {n} punti</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="str">
-        <v>↻ Regenerate</v>
-      </c>
-      <c r="B151" t="str">
         <v>↻ Rigenera</v>
+      </c>
+    </row>
+    <row r="151" xml:space="preserve">
+      <c r="A151" t="str" xml:space="preserve">
+        <v xml:space="preserve">Input
+colorant</v>
+      </c>
+      <c r="B151" t="str" xml:space="preserve">
+        <v xml:space="preserve">Colorante
+ingresso</v>
       </c>
     </row>
     <row r="152" xml:space="preserve">
       <c r="A152" t="str" xml:space="preserve">
-        <v xml:space="preserve">Input
-colorant</v>
-      </c>
-      <c r="B152" t="str" xml:space="preserve">
-        <v xml:space="preserve">Colorante
-ingresso</v>
-      </c>
-    </row>
-    <row r="153" xml:space="preserve">
-      <c r="A153" t="str" xml:space="preserve">
         <v xml:space="preserve">Nearest
 in dataset</v>
       </c>
-      <c r="B153" t="str" xml:space="preserve">
+      <c r="B152" t="str" xml:space="preserve">
         <v xml:space="preserve">Più vicino
 nel set</v>
       </c>
     </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>Model</v>
+      </c>
+      <c r="B153" t="str">
+        <v>Modello</v>
+      </c>
+    </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Model</v>
+        <v>Computing…</v>
       </c>
       <c r="B154" t="str">
-        <v>Modello</v>
+        <v>Calcolo…</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Computing…</v>
+        <v>Calculating tone values…</v>
       </c>
       <c r="B155" t="str">
-        <v>Calcolo…</v>
+        <v>Calculating tone values…</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Calculating tone values…</v>
+        <v>Estimating model…</v>
       </c>
       <c r="B156" t="str">
-        <v>Calculating tone values…</v>
+        <v>Estimating model…</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Estimating model…</v>
+        <v>Building 3D gamut…</v>
       </c>
       <c r="B157" t="str">
-        <v>Estimating model…</v>
+        <v>Building 3D gamut…</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Building 3D gamut…</v>
+        <v>Computing 2D slice…</v>
       </c>
       <c r="B158" t="str">
-        <v>Building 3D gamut…</v>
+        <v>Computing 2D slice…</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Computing 2D slice…</v>
+        <v>Rendering…</v>
       </c>
       <c r="B159" t="str">
-        <v>Computing 2D slice…</v>
+        <v>Rendering…</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Rendering…</v>
+        <v>Model fit failed: {msg}</v>
       </c>
       <c r="B160" t="str">
-        <v>Rendering…</v>
+        <v>Adattamento modello fallito: {msg}</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Model fit failed: {msg}</v>
+        <v>Retry</v>
       </c>
       <c r="B161" t="str">
-        <v>Adattamento modello fallito: {msg}</v>
+        <v>Riprova</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Retry</v>
+        <v>Click on L*a*b* color to display spectral graph.</v>
       </c>
       <c r="B162" t="str">
-        <v>Riprova</v>
+        <v>Clicca su un colore L*a*b* per visualizzare il grafico spettrale.</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Click on L*a*b* color to display spectral graph.</v>
+        <v>Scroll to top</v>
       </c>
       <c r="B163" t="str">
-        <v>Clicca su un colore L*a*b* per visualizzare il grafico spettrale.</v>
+        <v>Torna su</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Scroll to top</v>
+        <v>Top</v>
       </c>
       <c r="B164" t="str">
-        <v>Torna su</v>
+        <v>Su</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Top</v>
+        <v>Help</v>
       </c>
       <c r="B165" t="str">
-        <v>Su</v>
+        <v>Guida</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Help</v>
+        <v>About CharData</v>
       </c>
       <c r="B166" t="str">
-        <v>Guida</v>
+        <v>Informazioni su CharData</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>About CharData</v>
+        <v>Support on Ko-fi</v>
       </c>
       <c r="B167" t="str">
-        <v>Informazioni su CharData</v>
+        <v>Sostieni su Ko-fi</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Support on Ko-fi</v>
+        <v>Buy me a coffee</v>
       </c>
       <c r="B168" t="str">
-        <v>Sostieni su Ko-fi</v>
+        <v>Offrimi un caffè</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Buy me a coffee</v>
+        <v>Reflectance</v>
       </c>
       <c r="B169" t="str">
-        <v>Offrimi un caffè</v>
+        <v>Riflettanza</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Reflectance</v>
+        <v>CharData is free for the color community. If it helps you, a small Ko-fi donation helps keep it running.</v>
       </c>
       <c r="B170" t="str">
-        <v>Riflettanza</v>
+        <v>CharData è gratuito per la comunità del colore. Un piccolo contributo Ko-fi aiuta a mantenerlo attivo.</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>CharData is free for the color community. If it helps you, a small Ko-fi donation helps keep it running.</v>
+        <v>Characterization data</v>
       </c>
       <c r="B171" t="str">
-        <v>CharData è gratuito per la comunità del colore. Un piccolo contributo Ko-fi aiuta a mantenerlo attivo.</v>
+        <v>Dati di caratterizzazione</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Characterization data</v>
+        <v>ICC Profiles</v>
       </c>
       <c r="B172" t="str">
-        <v>Dati di caratterizzazione</v>
+        <v>Profili ICC</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>ICC Profiles</v>
+        <v>No characterization datasets loaded</v>
       </c>
       <c r="B173" t="str">
-        <v>Profili ICC</v>
+        <v>Nessun dataset di caratterizzazione caricato</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>No characterization datasets loaded</v>
+        <v>No ICC profiles loaded</v>
       </c>
       <c r="B174" t="str">
-        <v>Nessun dataset di caratterizzazione caricato</v>
+        <v>Nessun profilo ICC caricato</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>No ICC profiles loaded</v>
+        <v>Characterization dataset</v>
       </c>
       <c r="B175" t="str">
-        <v>Nessun profilo ICC caricato</v>
+        <v>Dataset di caratterizzazione</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Characterization dataset</v>
+        <v>ICC Profile</v>
       </c>
       <c r="B176" t="str">
-        <v>Dataset di caratterizzazione</v>
+        <v>Profilo ICC</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>ICC Profile</v>
+        <v>Not a valid ICC profile (header magic missing).</v>
       </c>
       <c r="B177" t="str">
-        <v>Profilo ICC</v>
+        <v>Profilo ICC non valido (signature dell’header mancante).</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Not a valid ICC profile (header magic missing).</v>
+        <v>Standard datasets</v>
       </c>
       <c r="B178" t="str">
-        <v>Profilo ICC non valido (signature dell’header mancante).</v>
+        <v>Set di dati standard</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Standard datasets</v>
+        <v>Loading…</v>
       </c>
       <c r="B179" t="str">
-        <v>Set di dati standard</v>
+        <v>Caricamento…</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Loading…</v>
+        <v>Failed to load list</v>
       </c>
       <c r="B180" t="str">
-        <v>Caricamento…</v>
+        <v>Caricamento dell'elenco non riuscito</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Failed to load list</v>
+        <v>Thickness:</v>
       </c>
       <c r="B181" t="str">
-        <v>Caricamento dell'elenco non riuscito</v>
+        <v>Spessore:</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Thickness:</v>
+        <v>Fall-off:</v>
       </c>
       <c r="B182" t="str">
-        <v>Spessore:</v>
+        <v>Attenuazione:</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Fall-off:</v>
+        <v>Hard</v>
       </c>
       <c r="B183" t="str">
-        <v>Attenuazione:</v>
+        <v>Netto</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Hard</v>
+        <v>Soft</v>
       </c>
       <c r="B184" t="str">
-        <v>Netto</v>
+        <v>Morbido</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Soft</v>
+        <v>G7 validation is not available for ICC profiles.</v>
       </c>
       <c r="B185" t="str">
-        <v>Morbido</v>
+        <v>La validazione G7 non è disponibile per i profili ICC.</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>G7 validation is not available for ICC profiles.</v>
+        <v>ICC vs ICC comparison requires identical colorant lists. Profile A: {a}. Profile B: {b}.</v>
       </c>
       <c r="B186" t="str">
-        <v>La validazione G7 non è disponibile per i profili ICC.</v>
+        <v>Il confronto ICC vs ICC richiede liste di coloranti identiche. Profilo A: {a}. Profilo B: {b}.</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>ICC vs ICC comparison requires identical colorant lists. Profile A: {a}. Profile B: {b}.</v>
+        <v>Dataset B does not contain colorants matching ICC profile A.</v>
       </c>
       <c r="B187" t="str">
-        <v>Il confronto ICC vs ICC richiede liste di coloranti identiche. Profilo A: {a}. Profilo B: {b}.</v>
+        <v>Il dataset B non contiene coloranti corrispondenti al profilo ICC A.</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Dataset B does not contain colorants matching ICC profile A.</v>
+        <v>Dataset A does not contain colorants matching ICC profile B.</v>
       </c>
       <c r="B188" t="str">
-        <v>Il dataset B non contiene coloranti corrispondenti al profilo ICC A.</v>
+        <v>Il dataset A non contiene coloranti corrispondenti al profilo ICC B.</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Dataset A does not contain colorants matching ICC profile B.</v>
+        <v>Header</v>
       </c>
       <c r="B189" t="str">
-        <v>Il dataset A non contiene coloranti corrispondenti al profilo ICC B.</v>
+        <v>Intestazione</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Header</v>
+        <v>Tags</v>
       </c>
       <c r="B190" t="str">
-        <v>Intestazione</v>
+        <v>Tag</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Tags</v>
+        <v>Loading ICC viewer…</v>
       </c>
       <c r="B191" t="str">
-        <v>Tag</v>
+        <v>Caricamento del visualizzatore ICC…</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Loading ICC viewer…</v>
+        <v>Launch editor</v>
       </c>
       <c r="B192" t="str">
-        <v>Caricamento del visualizzatore ICC…</v>
+        <v>Apri editor</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Launch editor</v>
+        <v>All data stays local to browser</v>
       </c>
       <c r="B193" t="str">
-        <v>Apri editor</v>
+        <v>Tutti i dati restano locali nel browser</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>All data stays local to browser</v>
+        <v>Free browser-resident online tool</v>
       </c>
       <c r="B194" t="str">
-        <v>Tutti i dati restano locali nel browser</v>
+        <v>Strumento online gratuito che funziona nel browser</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Free browser-resident online tool</v>
+        <v>Image</v>
       </c>
       <c r="B195" t="str">
-        <v>Strumento online gratuito che funziona nel browser</v>
+        <v>Immagine</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Image</v>
+        <v>Load Image</v>
       </c>
       <c r="B196" t="str">
-        <v>Immagine</v>
+        <v>Carica immagine</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Load Image</v>
+        <v>Bind image to dataset</v>
       </c>
       <c r="B197" t="str">
-        <v>Carica immagine</v>
+        <v>Associa l’immagine al dataset</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Bind image to dataset</v>
+        <v>Remove image</v>
       </c>
       <c r="B198" t="str">
-        <v>Associa l’immagine al dataset</v>
+        <v>Rimuovi immagine</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Remove image</v>
+        <v>Image color space: {cs} {src}</v>
       </c>
       <c r="B199" t="str">
-        <v>Rimuovi immagine</v>
+        <v>Spazio colore immagine: {cs} {src}</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Image color space: {cs} {src}</v>
+        <v>Bound to {name} — {n} points</v>
       </c>
       <c r="B200" t="str">
-        <v>Spazio colore immagine: {cs} {src}</v>
+        <v>Associato a {name} — {n} punti</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Bound to {name} — {n} points</v>
+        <v>Lab image — {n} points</v>
       </c>
       <c r="B201" t="str">
-        <v>Associato a {name} — {n} punti</v>
+        <v>Immagine Lab — {n} punti</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Lab image — {n} points</v>
+        <v>Cannot bind: image is {img} but Dataset {slot} is {family}.</v>
       </c>
       <c r="B202" t="str">
-        <v>Immagine Lab — {n} punti</v>
+        <v>Associazione impossibile: l’immagine è {img} ma il Dataset {slot} è {family}.</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Cannot bind: image is {img} but Dataset {slot} is {family}.</v>
+        <v>Unsupported image format. Use PNG, JPEG, TIFF, BMP, GIF, or PDF.</v>
       </c>
       <c r="B203" t="str">
-        <v>Associazione impossibile: l’immagine è {img} ma il Dataset {slot} è {family}.</v>
+        <v>Formato immagine non supportato. Usa PNG, JPEG, TIFF, BMP, GIF o PDF.</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Unsupported image format. Use PNG, JPEG, TIFF, BMP, GIF, or PDF.</v>
+        <v>“{name}” is too large ({mb} MB). Maximum image size is {max} MB.</v>
       </c>
       <c r="B204" t="str">
-        <v>Formato immagine non supportato. Usa PNG, JPEG, TIFF, BMP, GIF o PDF.</v>
+        <v>“{name}” è troppo grande ({mb} MB). Dimensione massima: {max} MB.</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>“{name}” is too large ({mb} MB). Maximum image size is {max} MB.</v>
+        <v>Embedded: {name}</v>
       </c>
       <c r="B205" t="str">
-        <v>“{name}” è troppo grande ({mb} MB). Dimensione massima: {max} MB.</v>
+        <v>Incorporato: {name}</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Embedded: {name}</v>
+        <v>Decoding image…</v>
       </c>
       <c r="B206" t="str">
-        <v>Incorporato: {name}</v>
+        <v>Decodifica immagine in corso…</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Decoding image…</v>
+        <v>Image file is too small or corrupt.</v>
       </c>
       <c r="B207" t="str">
-        <v>Decodifica immagine in corso…</v>
+        <v>Il file immagine è troppo piccolo o danneggiato.</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>Image file is too small or corrupt.</v>
+        <v>TIFF decoder library failed to load.</v>
       </c>
       <c r="B208" t="str">
-        <v>Il file immagine è troppo piccolo o danneggiato.</v>
+        <v>Caricamento della libreria di decodifica TIFF non riuscito.</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>TIFF decoder library failed to load.</v>
+        <v>Selected dataset model is still loading — try again in a moment.</v>
       </c>
       <c r="B209" t="str">
-        <v>Caricamento della libreria di decodifica TIFF non riuscito.</v>
+        <v>Il modello del dataset selezionato è ancora in caricamento — riprova tra un istante.</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>Selected dataset model is still loading — try again in a moment.</v>
+        <v>Image decode failed.</v>
       </c>
       <c r="B210" t="str">
-        <v>Il modello del dataset selezionato è ancora in caricamento — riprova tra un istante.</v>
+        <v>Decodifica immagine non riuscita.</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>Image decode failed.</v>
+        <v>No color dataset loaded.</v>
       </c>
       <c r="B211" t="str">
-        <v>Decodifica immagine non riuscita.</v>
+        <v>Nessun set di dati colorimetrici caricato.</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>No color dataset loaded.</v>
+        <v>Embedded profile is no longer available.</v>
       </c>
       <c r="B212" t="str">
-        <v>Nessun set di dati colorimetrici caricato.</v>
+        <v>Il profilo incorporato non è più disponibile.</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>Embedded profile is no longer available.</v>
+        <v>(from embedded ICC)</v>
       </c>
       <c r="B213" t="str">
-        <v>Il profilo incorporato non è più disponibile.</v>
+        <v>(dall’ICC incorporato)</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>(from embedded ICC)</v>
+        <v>(TIFF Lab)</v>
       </c>
       <c r="B214" t="str">
-        <v>(dall’ICC incorporato)</v>
+        <v>(TIFF Lab)</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>(TIFF Lab)</v>
+        <v>(inferred from channels)</v>
       </c>
       <c r="B215" t="str">
-        <v>(TIFF Lab)</v>
+        <v>(dedotto dai canali)</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>(inferred from channels)</v>
+        <v>{n} representative points after binning + dedupe</v>
       </c>
       <c r="B216" t="str">
-        <v>(dedotto dai canali)</v>
+        <v>{n} punti rappresentativi dopo binning + deduplica</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>{n} representative points after binning + dedupe</v>
+        <v>PDF support is limited to single-image Photoshop PDFs. Save as TIFF, JPEG, PNG, BMP, or GIF for other PDF content.</v>
       </c>
       <c r="B217" t="str">
-        <v>{n} punti rappresentativi dopo binning + deduplica</v>
+        <v>Il supporto PDF è limitato ai PDF Photoshop con una sola immagine. Salva come TIFF, JPEG, PNG, BMP o GIF per altri contenuti PDF.</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>PDF support is limited to single-image Photoshop PDFs. Save as TIFF, JPEG, PNG, BMP, or GIF for other PDF content.</v>
+        <v>Encrypted PDFs are not supported.</v>
       </c>
       <c r="B218" t="str">
-        <v>Il supporto PDF è limitato ai PDF Photoshop con una sola immagine. Salva come TIFF, JPEG, PNG, BMP o GIF per altri contenuti PDF.</v>
+        <v>I PDF crittografati non sono supportati.</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>Encrypted PDFs are not supported.</v>
+        <v>Only single-page Photoshop PDFs are supported.</v>
       </c>
       <c r="B219" t="str">
-        <v>I PDF crittografati non sono supportati.</v>
+        <v>Sono supportati solo i PDF Photoshop di una sola pagina.</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>Only single-page Photoshop PDFs are supported.</v>
+        <v>PDF structure could not be parsed.</v>
       </c>
       <c r="B220" t="str">
-        <v>Sono supportati solo i PDF Photoshop di una sola pagina.</v>
+        <v>Impossibile analizzare la struttura del PDF.</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>PDF structure could not be parsed.</v>
+        <v>No image found inside the PDF.</v>
       </c>
       <c r="B221" t="str">
-        <v>Impossibile analizzare la struttura del PDF.</v>
+        <v>Nessuna immagine trovata nel PDF.</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>No image found inside the PDF.</v>
+        <v>PDF colour space is not supported. Use Gray, RGB, CMYK, or an ICC-based profile.</v>
       </c>
       <c r="B222" t="str">
-        <v>Nessuna immagine trovata nel PDF.</v>
+        <v>Spazio colore PDF non supportato. Usa Grigio, RGB, CMYK o un profilo ICC.</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>PDF colour space is not supported. Use Gray, RGB, CMYK, or an ICC-based profile.</v>
+        <v>PDF image filter is not supported. Re-save the PDF with JPEG or ZIP compression.</v>
       </c>
       <c r="B223" t="str">
-        <v>Spazio colore PDF non supportato. Usa Grigio, RGB, CMYK o un profilo ICC.</v>
+        <v>Filtro immagine PDF non supportato. Salva nuovamente il PDF con compressione JPEG o ZIP.</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>PDF image filter is not supported. Re-save the PDF with JPEG or ZIP compression.</v>
+        <v>Close file select</v>
       </c>
       <c r="B224" t="str">
-        <v>Filtro immagine PDF non supportato. Salva nuovamente il PDF con compressione JPEG o ZIP.</v>
+        <v>Chiudi selezione file</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>Close file select</v>
+        <v>Drag to resize</v>
       </c>
       <c r="B225" t="str">
-        <v>Chiudi selezione file</v>
+        <v>Trascina per ridimensionare</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>Drag to resize</v>
+        <v>Contact</v>
       </c>
       <c r="B226" t="str">
-        <v>Trascina per ridimensionare</v>
+        <v>Contatto</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Contact</v>
+        <v>Remove file</v>
       </c>
       <c r="B227" t="str">
-        <v>Contatto</v>
+        <v>Rimuovi file</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>Remove file</v>
+        <v>Rendering intent:</v>
       </c>
       <c r="B228" t="str">
-        <v>Rimuovi file</v>
+        <v>Intento di rendering:</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>Rendering intent:</v>
+        <v>Perceptual</v>
       </c>
       <c r="B229" t="str">
-        <v>Intento di rendering:</v>
+        <v>Percettivo</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>Perceptual</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B230" t="str">
-        <v>Percettivo</v>
+        <v>Colorimetrico relativo</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Saturation</v>
       </c>
       <c r="B231" t="str">
-        <v>Colorimetrico relativo</v>
+        <v>Saturazione</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>Saturation</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B232" t="str">
-        <v>Saturazione</v>
+        <v>Colorimetrico assoluto</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>System default ({lang})</v>
       </c>
       <c r="B233" t="str">
-        <v>Colorimetrico assoluto</v>
+        <v>Predefinito di sistema ({lang})</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>System default ({lang})</v>
+        <v>ICC load error: {msg}</v>
       </c>
       <c r="B234" t="str">
-        <v>Predefinito di sistema ({lang})</v>
+        <v>Errore di caricamento ICC: {msg}</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>ICC load error: {msg}</v>
+        <v>Could not parse ICC profile: {msg}</v>
       </c>
       <c r="B235" t="str">
-        <v>Errore di caricamento ICC: {msg}</v>
+        <v>Impossibile analizzare il profilo ICC: {msg}</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>Could not parse ICC profile: {msg}</v>
+        <v>Popup blocked — allow popups for this site to launch the editor.</v>
       </c>
       <c r="B236" t="str">
-        <v>Impossibile analizzare il profilo ICC: {msg}</v>
+        <v>Popup bloccato — consenti i popup per questo sito per avviare l’editor.</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>Popup blocked — allow popups for this site to launch the editor.</v>
+        <v>Failed to load {name}: {msg}</v>
       </c>
       <c r="B237" t="str">
-        <v>Popup bloccato — consenti i popup per questo sito per avviare l’editor.</v>
+        <v>Caricamento di {name} non riuscito: {msg}</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>Failed to load {name}: {msg}</v>
+        <v>Color space</v>
       </c>
       <c r="B238" t="str">
-        <v>Caricamento di {name} non riuscito: {msg}</v>
+        <v>Spazio colore</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>Color space</v>
+        <v>Device class</v>
       </c>
       <c r="B239" t="str">
-        <v>Spazio colore</v>
+        <v>Classe dispositivo</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>Device class</v>
+        <v>Colorants</v>
       </c>
       <c r="B240" t="str">
-        <v>Classe dispositivo</v>
+        <v>Coloranti</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>Colorants</v>
+        <v>Rendering intents</v>
       </c>
       <c r="B241" t="str">
-        <v>Coloranti</v>
+        <v>Intenti di rendering</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>Rendering intents</v>
+        <v>ICC A2B Evaluation</v>
       </c>
       <c r="B242" t="str">
-        <v>Intenti di rendering</v>
+        <v>Valutazione ICC A2B</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>ICC A2B Evaluation</v>
+        <v>ICC Output</v>
       </c>
       <c r="B243" t="str">
-        <v>Valutazione ICC A2B</v>
+        <v>Uscita ICC</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>ICC Output</v>
+        <v>Image detail</v>
       </c>
       <c r="B244" t="str">
-        <v>Uscita ICC</v>
+        <v>Dettaglio immagine</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>Image detail</v>
+        <v>Coarse</v>
       </c>
       <c r="B245" t="str">
-        <v>Dettaglio immagine</v>
+        <v>Grossolano</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>Coarse</v>
+        <v>Standard</v>
       </c>
       <c r="B246" t="str">
-        <v>Grossolano</v>
+        <v>Standard</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>Standard</v>
+        <v>Fine</v>
       </c>
       <c r="B247" t="str">
-        <v>Standard</v>
+        <v>Fine</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>Fine</v>
+        <v>Subscribe</v>
       </c>
       <c r="B248" t="str">
-        <v>Fine</v>
+        <v>Iscriviti</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>Subscribe</v>
+        <v>Get notified about new chardata releases</v>
       </c>
       <c r="B249" t="str">
-        <v>Iscriviti</v>
+        <v>Ricevi notifiche sulle nuove versioni di chardata</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>Get notified about new chardata releases</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B250" t="str">
-        <v>Ricevi notifiche sulle nuove versioni di chardata</v>
+        <v>Ricevi notifiche sulle nuove versioni</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>Get notified about new releases</v>
+        <v>Close</v>
       </c>
       <c r="B251" t="str">
-        <v>Ricevi notifiche sulle nuove versioni</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>Close</v>
+        <v>We’ll email you when a new major or minor chardata release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B252" t="str">
-        <v>Chiudi</v>
+        <v>Ti invieremo un’e-mail quando esce una nuova versione maggiore o minore di chardata. Le versioni patch sono escluse. Il tuo indirizzo viene verificato manualmente prima di essere aggiunto.</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>We’ll email you when a new major or minor chardata release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Email address</v>
       </c>
       <c r="B253" t="str">
-        <v>Ti invieremo un’e-mail quando esce una nuova versione maggiore o minore di chardata. Le versioni patch sono escluse. Il tuo indirizzo viene verificato manualmente prima di essere aggiunto.</v>
+        <v>Indirizzo e-mail</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>Email address</v>
+        <v>you@example.com</v>
       </c>
       <c r="B254" t="str">
-        <v>Indirizzo e-mail</v>
+        <v>tu@esempio.com</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>you@example.com</v>
+        <v>How will you use chardata?</v>
       </c>
       <c r="B255" t="str">
-        <v>tu@esempio.com</v>
+        <v>Come utilizzerai chardata?</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>How will you use chardata?</v>
+        <v>(optional)</v>
       </c>
       <c r="B256" t="str">
-        <v>Come utilizzerai chardata?</v>
+        <v>(opzionale)</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>(optional)</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B257" t="str">
-        <v>(opzionale)</v>
+        <v>p. es. valutare profili ICC per la calibrazione di stampa</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>I agree to receive emails about chardata releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B258" t="str">
-        <v>p. es. valutare profili ICC per la calibrazione di stampa</v>
+        <v>Accetto di ricevere e-mail sulle versioni di chardata. Posso annullare l’iscrizione in qualsiasi momento.</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>I agree to receive emails about chardata releases. I can unsubscribe at any time.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B259" t="str">
-        <v>Accetto di ricevere e-mail sulle versioni di chardata. Posso annullare l’iscrizione in qualsiasi momento.</v>
+        <v>Iscriviti</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>Subscribe</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B260" t="str">
-        <v>Iscriviti</v>
+        <v>Grazie — ti ricontatteremo.</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new chardata release ships.</v>
       </c>
       <c r="B261" t="str">
-        <v>Grazie — ti ricontatteremo.</v>
+        <v>Una volta approvato, riceverai un’e-mail di benvenuto. In seguito, ti contatteremo solo quando uscirà una nuova versione di chardata.</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new chardata release ships.</v>
+        <v>Close</v>
       </c>
       <c r="B262" t="str">
-        <v>Una volta approvato, riceverai un’e-mail di benvenuto. In seguito, ti contatteremo solo quando uscirà una nuova versione di chardata.</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>Close</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B263" t="str">
-        <v>Chiudi</v>
+        <v>Informativa sulla privacy</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>Privacy notice</v>
+        <v>Measurement-only data (no device colorants): 3D and 2D-slice point cloud, data table, and label-matched compare are available; gamut shell, extract, tone value, estimate, and validation are disabled.</v>
       </c>
       <c r="B264" t="str">
-        <v>Informativa sulla privacy</v>
+        <v>Solo dati di misura (nessun colorante dispositivo): nuvola di punti 3D e sezione 2D, tabella dati e confronto per etichetta disponibili; guscio gamut, estrazione, valore di tono, stima e validazione disabilitati.</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>Measurement-only data (no device colorants): 3D and 2D-slice point cloud, data table, and label-matched compare are available; gamut shell, extract, tone value, estimate, and validation are disabled.</v>
+        <v>Sample</v>
       </c>
       <c r="B265" t="str">
-        <v>Solo dati di misura (nessun colorante dispositivo): nuvola di punti 3D e sezione 2D, tabella dati e confronto per etichetta disponibili; guscio gamut, estrazione, valore di tono, stima e validazione disabilitati.</v>
+        <v>Campione</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>Sample</v>
+        <v>CxF file is not well-formed XML.</v>
       </c>
       <c r="B266" t="str">
-        <v>Campione</v>
+        <v>Il file CxF non è un XML ben formato.</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>CxF file is not well-formed XML.</v>
+        <v>CxF file contains no colour objects.</v>
       </c>
       <c r="B267" t="str">
-        <v>Il file CxF non è un XML ben formato.</v>
+        <v>Il file CxF non contiene oggetti colore.</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>CxF file contains no colour objects.</v>
+        <v>CxF file contains no CIELab or spectral colour values.</v>
       </c>
       <c r="B268" t="str">
-        <v>Il file CxF non contiene oggetti colore.</v>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="str">
-        <v>CxF file contains no CIELab or spectral colour values.</v>
-      </c>
-      <c r="B269" t="str">
         <v>Il file CxF non contiene valori di colore CIELab o spettrali.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B269"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B268"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B268"/>
+  <dimension ref="A1:B270"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2551,9 +2551,25 @@
         <v>Il file CxF non contiene valori di colore CIELab o spettrali.</v>
       </c>
     </row>
+    <row r="269">
+      <c r="A269" t="str">
+        <v>IT8.7/5 Patches ({n})</v>
+      </c>
+      <c r="B269" t="str">
+        <v>Patch IT8.7/5 ({n})</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="str">
+        <v>Device Patches ({n})</v>
+      </c>
+      <c r="B270" t="str">
+        <v>Patch dispositivo ({n})</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B268"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B270"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B270"/>
+  <dimension ref="A1:B273"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2567,9 +2567,33 @@
         <v>Patch dispositivo ({n})</v>
       </c>
     </row>
+    <row r="271">
+      <c r="A271" t="str">
+        <v>Number format</v>
+      </c>
+      <c r="B271" t="str">
+        <v>Formato numerico</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="str">
+        <v>Hexadecimal</v>
+      </c>
+      <c r="B272" t="str">
+        <v>Esadecimale</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="str">
+        <v>Decimal</v>
+      </c>
+      <c r="B273" t="str">
+        <v>Decimale</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B270"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B273"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B273"/>
+  <dimension ref="A1:B308"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2591,9 +2591,289 @@
         <v>Decimale</v>
       </c>
     </row>
+    <row r="274">
+      <c r="A274" t="str">
+        <v>Tag Name</v>
+      </c>
+      <c r="B274" t="str">
+        <v>Nome tag</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B275" t="str">
+        <v>ID</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="str">
+        <v>Type</v>
+      </c>
+      <c r="B276" t="str">
+        <v>Tipo</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="str">
+        <v>Offset</v>
+      </c>
+      <c r="B277" t="str">
+        <v>Offset</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="str">
+        <v>Size</v>
+      </c>
+      <c r="B278" t="str">
+        <v>Dimensione</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="str">
+        <v>Pad</v>
+      </c>
+      <c r="B279" t="str">
+        <v>Riempimento</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="str">
+        <v>No tags found.</v>
+      </c>
+      <c r="B280" t="str">
+        <v>Nessun tag trovato.</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="str">
+        <v>Array of</v>
+      </c>
+      <c r="B281" t="str">
+        <v>Array di</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="str">
+        <v>Profile ID</v>
+      </c>
+      <c r="B282" t="str">
+        <v>ID profilo</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="str">
+        <v>Loading full description…</v>
+      </c>
+      <c r="B283" t="str">
+        <v>Caricamento della descrizione completa…</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="str">
+        <v xml:space="preserve">Could not load full description: </v>
+      </c>
+      <c r="B284" t="str">
+        <v xml:space="preserve">Impossibile caricare la descrizione completa: </v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="str">
+        <v>(No content)</v>
+      </c>
+      <c r="B285" t="str">
+        <v>(Nessun contenuto)</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="str">
+        <v>Neutral = in gamut</v>
+      </c>
+      <c r="B286" t="str">
+        <v>Neutro = nel gamut</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="str">
+        <v>Red = out of gamut</v>
+      </c>
+      <c r="B287" t="str">
+        <v>Rosso = fuori gamut</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="str">
+        <v>No CLUT grid</v>
+      </c>
+      <c r="B288" t="str">
+        <v>Nessuna griglia CLUT</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="str">
+        <v>Float</v>
+      </c>
+      <c r="B289" t="str">
+        <v>Virgola mobile</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="str">
+        <v>Grid</v>
+      </c>
+      <c r="B290" t="str">
+        <v>Griglia</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="str">
+        <v>PCS → Device</v>
+      </c>
+      <c r="B291" t="str">
+        <v>PCS → Dispositivo</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="str">
+        <v>Device → PCS</v>
+      </c>
+      <c r="B292" t="str">
+        <v>Dispositivo → PCS</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="str">
+        <v>Input</v>
+      </c>
+      <c r="B293" t="str">
+        <v>Ingresso</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="str">
+        <v>Output</v>
+      </c>
+      <c r="B294" t="str">
+        <v>Uscita</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="str">
+        <v>Human</v>
+      </c>
+      <c r="B295" t="str">
+        <v>Leggibile</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="str">
+        <v>Norm</v>
+      </c>
+      <c r="B296" t="str">
+        <v>Norm.</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="str">
+        <v>Chromaticity</v>
+      </c>
+      <c r="B297" t="str">
+        <v>Cromaticità</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="str">
+        <v>Tone curve</v>
+      </c>
+      <c r="B298" t="str">
+        <v>Curva di tono</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="str">
+        <v>Curve table</v>
+      </c>
+      <c r="B299" t="str">
+        <v>Tabella curva</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="str">
+        <v>Scatter</v>
+      </c>
+      <c r="B300" t="str">
+        <v>Dispersione</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="str">
+        <v>Tables</v>
+      </c>
+      <c r="B301" t="str">
+        <v>Tabelle</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="str">
+        <v>Curves</v>
+      </c>
+      <c r="B302" t="str">
+        <v>Curve</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="str">
+        <v>Input curves</v>
+      </c>
+      <c r="B303" t="str">
+        <v>Curve di ingresso</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="str">
+        <v>Output curves</v>
+      </c>
+      <c r="B304" t="str">
+        <v>Curve di uscita</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="str">
+        <v>CLUT</v>
+      </c>
+      <c r="B305" t="str">
+        <v>CLUT</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="str">
+        <v>Gamut</v>
+      </c>
+      <c r="B306" t="str">
+        <v>Gamut</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="str">
+        <v>Evaluate</v>
+      </c>
+      <c r="B307" t="str">
+        <v>Valuta</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="str">
+        <v>Data</v>
+      </c>
+      <c r="B308" t="str">
+        <v>Dati</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B273"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B308"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B308"/>
+  <dimension ref="A1:B309"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2871,9 +2871,17 @@
         <v>Dati</v>
       </c>
     </row>
+    <row r="309">
+      <c r="A309" t="str">
+        <v>Spot ink characterisation (CxF/X-4): tint levels are loaded as device colorant values; gamut shell, estimate, and model generation are disabled.</v>
+      </c>
+      <c r="B309" t="str">
+        <v>Caratterizzazione di inchiostro spot (CxF/X-4): i livelli di tinta sono caricati come valori di colorante dispositivo; guscio gamut, stima e generazione del modello disabilitati.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B308"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B309"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B309"/>
+  <dimension ref="A1:B310"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2879,9 +2879,17 @@
         <v>Caratterizzazione di inchiostro spot (CxF/X-4): i livelli di tinta sono caricati come valori di colorante dispositivo; guscio gamut, stima e generazione del modello disabilitati.</v>
       </c>
     </row>
+    <row r="310">
+      <c r="A310" t="str">
+        <v>Reset zoom</v>
+      </c>
+      <c r="B310" t="str">
+        <v>Reimposta zoom</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B309"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B310"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B310"/>
+  <dimension ref="A1:B315"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2887,9 +2887,49 @@
         <v>Reimposta zoom</v>
       </c>
     </row>
+    <row r="311">
+      <c r="A311" t="str">
+        <v>Colorimetry Source</v>
+      </c>
+      <c r="B311" t="str">
+        <v>Sorgente colorimetrica</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="str">
+        <v>Prefer spectral</v>
+      </c>
+      <c r="B312" t="str">
+        <v>Preferisci spettrale</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="str">
+        <v>Use file LAB</v>
+      </c>
+      <c r="B313" t="str">
+        <v>Usa LAB del file</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="str">
+        <v>File has both spectral and LAB; using LAB computed from spectral per preference.</v>
+      </c>
+      <c r="B314" t="str">
+        <v>Il file contiene spettrale e LAB; LAB calcolato dallo spettrale secondo la preferenza.</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="str">
+        <v>File has both spectral and LAB; using the file’s LAB per preference.</v>
+      </c>
+      <c r="B315" t="str">
+        <v>Il file contiene spettrale e LAB; uso del LAB del file secondo la preferenza.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B310"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B315"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B315"/>
+  <dimension ref="A1:B319"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2927,9 +2927,41 @@
         <v>Il file contiene spettrale e LAB; uso del LAB del file secondo la preferenza.</v>
       </c>
     </row>
+    <row r="316">
+      <c r="A316" t="str">
+        <v>Zoom in</v>
+      </c>
+      <c r="B316" t="str">
+        <v>Ingrandisci</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="str">
+        <v>Zoom out</v>
+      </c>
+      <c r="B317" t="str">
+        <v>Riduci</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="str">
+        <v>Reset to fit</v>
+      </c>
+      <c r="B318" t="str">
+        <v>Ripristina adattamento</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="str">
+        <v>Drag to resize</v>
+      </c>
+      <c r="B319" t="str">
+        <v>Trascina per ridimensionare</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B315"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B319"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B319"/>
+  <dimension ref="A1:B320"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2959,9 +2959,17 @@
         <v>Trascina per ridimensionare</v>
       </c>
     </row>
+    <row r="320">
+      <c r="A320" t="str">
+        <v>Show gamut wireframe</v>
+      </c>
+      <c r="B320" t="str">
+        <v>Mostra reticolo gamut</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B319"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B320"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B320"/>
+  <dimension ref="A1:B327"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2967,9 +2967,65 @@
         <v>Mostra reticolo gamut</v>
       </c>
     </row>
+    <row r="321">
+      <c r="A321" t="str">
+        <v>Comparison Statistics</v>
+      </c>
+      <c r="B321" t="str">
+        <v>Statistiche di confronto</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="str">
+        <v>Relative frequency</v>
+      </c>
+      <c r="B322" t="str">
+        <v>Frequenza relativa</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="str">
+        <v>Cumulative frequency</v>
+      </c>
+      <c r="B323" t="str">
+        <v>Frequenza cumulata</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="str">
+        <v>Horizontal scale</v>
+      </c>
+      <c r="B324" t="str">
+        <v>Scala orizzontale</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="str">
+        <v>Integer ΔE</v>
+      </c>
+      <c r="B325" t="str">
+        <v>ΔE intero</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="str">
+        <v>Auto-scale</v>
+      </c>
+      <c r="B326" t="str">
+        <v>Scala automatica</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="str">
+        <v>Bins</v>
+      </c>
+      <c r="B327" t="str">
+        <v>Intervalli</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B320"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B327"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B327"/>
+  <dimension ref="A1:B334"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3023,9 +3023,65 @@
         <v>Intervalli</v>
       </c>
     </row>
+    <row r="328">
+      <c r="A328" t="str">
+        <v>Rotation</v>
+      </c>
+      <c r="B328" t="str">
+        <v>Rotazione</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="str">
+        <v>Mode:</v>
+      </c>
+      <c r="B329" t="str">
+        <v>Modalità:</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="str">
+        <v>Turntable</v>
+      </c>
+      <c r="B330" t="str">
+        <v>Piattaforma</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="str">
+        <v>Orbit</v>
+      </c>
+      <c r="B331" t="str">
+        <v>Orbita</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="str">
+        <v>Drag rotate sensitivity:</v>
+      </c>
+      <c r="B332" t="str">
+        <v>Sensibilità rotazione (trascinamento):</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="str">
+        <v>Enable roll (horizontal scroll)</v>
+      </c>
+      <c r="B333" t="str">
+        <v>Abilita rollio (scorrimento orizzontale)</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="str">
+        <v>Roll sensitivity:</v>
+      </c>
+      <c r="B334" t="str">
+        <v>Sensibilità rollio:</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B327"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B334"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B334"/>
+  <dimension ref="A1:B377"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3079,9 +3079,353 @@
         <v>Sensibilità rollio:</v>
       </c>
     </row>
+    <row r="335">
+      <c r="A335" t="str">
+        <v>Primaries &amp; Overprints</v>
+      </c>
+      <c r="B335" t="str">
+        <v>Primarie e sovrastampe</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="str">
+        <v>Patch</v>
+      </c>
+      <c r="B336" t="str">
+        <v>Campione</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="str">
+        <v>Paper</v>
+      </c>
+      <c r="B337" t="str">
+        <v>Carta</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="str">
+        <v>Cyan</v>
+      </c>
+      <c r="B338" t="str">
+        <v>Ciano</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="str">
+        <v>Magenta</v>
+      </c>
+      <c r="B339" t="str">
+        <v>Magenta</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="str">
+        <v>Yellow</v>
+      </c>
+      <c r="B340" t="str">
+        <v>Giallo</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="str">
+        <v>Black</v>
+      </c>
+      <c r="B341" t="str">
+        <v>Nero</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="str">
+        <v>Red</v>
+      </c>
+      <c r="B342" t="str">
+        <v>Rosso</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="str">
+        <v>Green</v>
+      </c>
+      <c r="B343" t="str">
+        <v>Verde</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="str">
+        <v>Blue</v>
+      </c>
+      <c r="B344" t="str">
+        <v>Blu</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="str">
+        <v>CMY</v>
+      </c>
+      <c r="B345" t="str">
+        <v>CMY</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="str">
+        <v>CMYK</v>
+      </c>
+      <c r="B346" t="str">
+        <v>CMYK</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="str">
+        <v>Found {n} duplicate measurements in the original dataset.</v>
+      </c>
+      <c r="B347" t="str">
+        <v>Trovate {n} misurazioni duplicate nel set di dati originale.</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="str">
+        <v>Found {n} duplicate measurements in the original dataset (repeatability ΔE mean {mean}, max {max}).</v>
+      </c>
+      <c r="B348" t="str">
+        <v>Trovate {n} misurazioni duplicate nel set di dati originale (ripetibilità ΔE media {mean}, max {max}).</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="str">
+        <v>Near-Neutral Survey</v>
+      </c>
+      <c r="B349" t="str">
+        <v>Analisi dei quasi-neutri</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="str">
+        <v>Threshold (ΔE*ab)</v>
+      </c>
+      <c r="B350" t="str">
+        <v>Soglia (ΔE*ab)</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="str">
+        <v>{near} of {total} patches within {thr} ΔE of neutral.</v>
+      </c>
+      <c r="B351" t="str">
+        <v>{near} campioni su {total} entro {thr} ΔE dal neutro.</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="str">
+        <v>No patches within {thr} ΔE of neutral.</v>
+      </c>
+      <c r="B352" t="str">
+        <v>Nessun campione entro {thr} ΔE dal neutro.</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="str">
+        <v>Distance from neutral (ΔE*ab)</v>
+      </c>
+      <c r="B353" t="str">
+        <v>Distanza dal neutro (ΔE*ab)</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="str">
+        <v>Near-neutral</v>
+      </c>
+      <c r="B354" t="str">
+        <v>Quasi-neutro</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="str">
+        <v>Other patches</v>
+      </c>
+      <c r="B355" t="str">
+        <v>Altri campioni</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="str">
+        <v>Comparison Plot</v>
+      </c>
+      <c r="B356" t="str">
+        <v>Grafico di confronto</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="str">
+        <v>P90 = {v}</v>
+      </c>
+      <c r="B357" t="str">
+        <v>P90 = {v}</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="str">
+        <v>Percentiles</v>
+      </c>
+      <c r="B358" t="str">
+        <v>Percentili</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="str">
+        <v>Per-channel ΔE</v>
+      </c>
+      <c r="B359" t="str">
+        <v>ΔE per canale</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="str">
+        <v>Included: patches using this ink (&gt;0). Excluded: patches without it. Only: this ink alone.</v>
+      </c>
+      <c r="B360" t="str">
+        <v>Incluse: campioni che usano questo inchiostro (&gt;0). Escluse: campioni senza. Solo: solo questo inchiostro.</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="str">
+        <v>Included</v>
+      </c>
+      <c r="B361" t="str">
+        <v>Incluse</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="str">
+        <v>Excluded</v>
+      </c>
+      <c r="B362" t="str">
+        <v>Escluse</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="str">
+        <v>Only</v>
+      </c>
+      <c r="B363" t="str">
+        <v>Solo</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="str">
+        <v>N</v>
+      </c>
+      <c r="B364" t="str">
+        <v>N</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="str">
+        <v>P90</v>
+      </c>
+      <c r="B365" t="str">
+        <v>P90</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="str">
+        <v>P95</v>
+      </c>
+      <c r="B366" t="str">
+        <v>P95</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="str">
+        <v>Max</v>
+      </c>
+      <c r="B367" t="str">
+        <v>Max</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="str">
+        <v>User Guide</v>
+      </c>
+      <c r="B368" t="str">
+        <v>Guida utente</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="str">
+        <v>Search the guide…</v>
+      </c>
+      <c r="B369" t="str">
+        <v>Cerca nella guida…</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="str">
+        <v>Previous match</v>
+      </c>
+      <c r="B370" t="str">
+        <v>Risultato precedente</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="str">
+        <v>Next match</v>
+      </c>
+      <c r="B371" t="str">
+        <v>Risultato successivo</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="str">
+        <v>Open in a new tab</v>
+      </c>
+      <c r="B372" t="str">
+        <v>Apri in una nuova scheda</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="str">
+        <v>Loading the guide…</v>
+      </c>
+      <c r="B373" t="str">
+        <v>Caricamento della guida…</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="str">
+        <v>Couldn’t load the guide. Try opening it in a new tab.</v>
+      </c>
+      <c r="B374" t="str">
+        <v>Impossibile caricare la guida. Prova ad aprirla in una nuova scheda.</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="str">
+        <v>No matches</v>
+      </c>
+      <c r="B375" t="str">
+        <v>Nessun risultato</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="str">
+        <v>{i}/{n}</v>
+      </c>
+      <c r="B376" t="str">
+        <v>{i}/{n}</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="str">
+        <v>Image is too large to process safely.</v>
+      </c>
+      <c r="B377" t="str">
+        <v>L’immagine è troppo grande per essere elaborata in sicurezza.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B334"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B377"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B377"/>
+  <dimension ref="A1:B386"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3423,9 +3423,81 @@
         <v>L’immagine è troppo grande per essere elaborata in sicurezza.</v>
       </c>
     </row>
+    <row r="378">
+      <c r="A378" t="str">
+        <v>L* Reversal</v>
+      </c>
+      <c r="B378" t="str">
+        <v>Inversione L*</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="str">
+        <v>Adding ink to a single-ink tint ramp should only darken it. Each measured ramp is checked; any step where L* rises is flagged as a reversal.</v>
+      </c>
+      <c r="B379" t="str">
+        <v>Aggiungere inchiostro a una rampa di tinta a inchiostro singolo dovrebbe solo scurirla. Ogni rampa misurata viene controllata; ogni passo in cui L* aumenta è segnalato come inversione.</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="str">
+        <v>Threshold (ΔL*)</v>
+      </c>
+      <c r="B380" t="str">
+        <v>Soglia (ΔL*)</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="str">
+        <v>{n} reversal(s) across {cols} ink ramp(s).</v>
+      </c>
+      <c r="B381" t="str">
+        <v>{n} inversione/i su {cols} rampa/e d’inchiostro.</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="str">
+        <v>No L* reversals — every ink ramp darkens monotonically.</v>
+      </c>
+      <c r="B382" t="str">
+        <v>Nessuna inversione di L* — ogni rampa d’inchiostro si scurisce in modo monotòno.</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="str">
+        <v>L* reversal</v>
+      </c>
+      <c r="B383" t="str">
+        <v>Inversione L*</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="str">
+        <v>Ink %</v>
+      </c>
+      <c r="B384" t="str">
+        <v>Inchiostro %</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="str">
+        <v>Colorant</v>
+      </c>
+      <c r="B385" t="str">
+        <v>Colorante</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="str">
+        <v>Ink range</v>
+      </c>
+      <c r="B386" t="str">
+        <v>Intervallo inchiostro</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B377"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B386"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B386"/>
+  <dimension ref="A1:B398"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3433,10 +3433,10 @@
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>Adding ink to a single-ink tint ramp should only darken it. Each measured ramp is checked; any step where L* rises is flagged as a reversal.</v>
+        <v>Adding ink to any one channel should only darken the print — whatever the other inks are set to. Each ink channel is checked against every background of the other inks; any pair where more ink gives a higher L* (a lighter result) is a reversal, flagging a measurement error, ink-limit / trapping artefact, or mislabelled patch.</v>
       </c>
       <c r="B379" t="str">
-        <v>Aggiungere inchiostro a una rampa di tinta a inchiostro singolo dovrebbe solo scurirla. Ogni rampa misurata viene controllata; ogni passo in cui L* aumenta è segnalato come inversione.</v>
+        <v>Aggiungere inchiostro a un singolo canale dovrebbe solo scurire la stampa — indipendentemente da come sono impostati gli altri inchiostri. Ogni canale d’inchiostro è controllato rispetto a ogni sfondo degli altri inchiostri; ogni coppia in cui più inchiostro dà un L* più alto (un risultato più chiaro) è un’inversione, che segnala un errore di misura, un artefatto di limite d’inchiostro / trapping o un patch etichettato male.</v>
       </c>
     </row>
     <row r="380">
@@ -3449,18 +3449,18 @@
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>{n} reversal(s) across {cols} ink ramp(s).</v>
+        <v>{n} reversal(s) above the threshold across {cols} ink channel(s).</v>
       </c>
       <c r="B381" t="str">
-        <v>{n} inversione/i su {cols} rampa/e d’inchiostro.</v>
+        <v>{n} inversione/i sopra la soglia su {cols} canale/i d’inchiostro.</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>No L* reversals — every ink ramp darkens monotonically.</v>
+        <v>No L* reversals above the threshold — every ink darkens monotonically across all backgrounds.</v>
       </c>
       <c r="B382" t="str">
-        <v>Nessuna inversione di L* — ogni rampa d’inchiostro si scurisce in modo monotòno.</v>
+        <v>Nessuna inversione di L* sopra la soglia — ogni inchiostro si scurisce in modo monotòno su tutti gli sfondi.</v>
       </c>
     </row>
     <row r="383">
@@ -3495,9 +3495,105 @@
         <v>Intervallo inchiostro</v>
       </c>
     </row>
+    <row r="387">
+      <c r="A387" t="str">
+        <v>Channel</v>
+      </c>
+      <c r="B387" t="str">
+        <v>Canale</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="str">
+        <v>Ink (low → high)</v>
+      </c>
+      <c r="B388" t="str">
+        <v>Inchiostro (basso → alto)</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="str">
+        <v>All</v>
+      </c>
+      <c r="B389" t="str">
+        <v>Tutti</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="str">
+        <v>Show more ({n})</v>
+      </c>
+      <c r="B390" t="str">
+        <v>Mostra altri ({n})</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="str">
+        <v>Per-channel summary</v>
+      </c>
+      <c r="B391" t="str">
+        <v>Riepilogo per canale</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="str">
+        <v>Samples</v>
+      </c>
+      <c r="B392" t="str">
+        <v>Campioni</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="str">
+        <v>Mean ΔL*</v>
+      </c>
+      <c r="B393" t="str">
+        <v>Media ΔL*</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="str">
+        <v>SD</v>
+      </c>
+      <c r="B394" t="str">
+        <v>DS</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="str">
+        <v>Max ΔL*</v>
+      </c>
+      <c r="B395" t="str">
+        <v>Max ΔL*</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="str">
+        <v># &gt; ε</v>
+      </c>
+      <c r="B396" t="str">
+        <v># &gt; ε</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="str">
+        <v>{pts} patches · {ramps} ramps examined · {rev} reversals</v>
+      </c>
+      <c r="B397" t="str">
+        <v>{pts} patch · {ramps} rampe esaminate · {rev} inversioni</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="str">
+        <v>Channels with many reversals list only the largest {n} by ΔL*.</v>
+      </c>
+      <c r="B398" t="str">
+        <v>I canali con molte inversioni mostrano solo le {n} maggiori per ΔL*.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B386"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B398"/>
   </ignoredErrors>
 </worksheet>
 </file>